--- a/prints/Acompanhamento 1on1 CCU.xlsx
+++ b/prints/Acompanhamento 1on1 CCU.xlsx
@@ -29,12 +29,12 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="00111111"/>
       <sz val="16"/>
     </font>
     <font>
       <i val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="00555555"/>
       <sz val="9"/>
     </font>
     <font>
@@ -106,7 +106,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C4122F"/>
+        <fgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
     <fill>
@@ -116,7 +116,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
+        <fgColor rgb="00C4122F"/>
       </patternFill>
     </fill>
     <fill>
@@ -135,13 +135,18 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
+    </border>
+    <border>
+      <bottom style="medium">
+        <color rgb="00C4122F"/>
+      </bottom>
     </border>
     <border>
       <left style="thin">
@@ -166,7 +171,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -177,64 +182,67 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -243,23 +251,23 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -357,11 +365,11 @@
   <oneCellAnchor>
     <from>
       <col>0</col>
-      <colOff>0</colOff>
+      <colOff>66675</colOff>
       <row>0</row>
-      <rowOff>0</rowOff>
+      <rowOff>66675</rowOff>
     </from>
-    <ext cx="2105025" cy="266700"/>
+    <ext cx="2562225" cy="323850"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -387,11 +395,11 @@
   <oneCellAnchor>
     <from>
       <col>0</col>
-      <colOff>0</colOff>
+      <colOff>66675</colOff>
       <row>0</row>
-      <rowOff>0</rowOff>
+      <rowOff>66675</rowOff>
     </from>
-    <ext cx="2105025" cy="266700"/>
+    <ext cx="2562225" cy="323850"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -417,11 +425,11 @@
   <oneCellAnchor>
     <from>
       <col>0</col>
-      <colOff>0</colOff>
+      <colOff>66675</colOff>
       <row>0</row>
-      <rowOff>0</rowOff>
+      <rowOff>66675</rowOff>
     </from>
-    <ext cx="2105025" cy="266700"/>
+    <ext cx="2562225" cy="323850"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -740,7 +748,7 @@
     <col width="52" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="34" customHeight="1">
+    <row r="1" ht="46" customHeight="1">
       <c r="A1" s="1" t="n"/>
       <c r="B1" s="1" t="n"/>
       <c r="C1" s="1" t="n"/>
@@ -794,113 +802,113 @@
           <t>0. CADASTRO (preencher na 1ª conversa, revisar depois)</t>
         </is>
       </c>
-      <c r="B5" s="1" t="n"/>
-      <c r="C5" s="1" t="n"/>
-      <c r="D5" s="1" t="n"/>
+      <c r="B5" s="8" t="n"/>
+      <c r="C5" s="8" t="n"/>
+      <c r="D5" s="8" t="n"/>
     </row>
     <row r="6" ht="46" customHeight="1">
-      <c r="A6" s="8" t="inlineStr"/>
-      <c r="B6" s="9" t="inlineStr">
+      <c r="A6" s="9" t="inlineStr"/>
+      <c r="B6" s="10" t="inlineStr">
         <is>
           <t>Curso, período e idade.</t>
         </is>
       </c>
-      <c r="C6" s="10" t="inlineStr">
+      <c r="C6" s="11" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="D6" s="11" t="inlineStr">
+      <c r="D6" s="12" t="inlineStr">
         <is>
           <t>Base do perfil; cruze com o momento de carreira.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="46" customHeight="1">
-      <c r="A7" s="12" t="inlineStr"/>
-      <c r="B7" s="13" t="inlineStr">
+      <c r="A7" s="13" t="inlineStr"/>
+      <c r="B7" s="14" t="inlineStr">
         <is>
           <t>Há quanto tempo está no clube.</t>
         </is>
       </c>
-      <c r="C7" s="14" t="inlineStr">
+      <c r="C7" s="15" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="D7" s="15" t="inlineStr">
+      <c r="D7" s="16" t="inlineStr">
         <is>
           <t>Tempo de casa calibra a expectativa de responsabilidade.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="46" customHeight="1">
-      <c r="A8" s="8" t="inlineStr"/>
-      <c r="B8" s="9" t="inlineStr">
+      <c r="A8" s="9" t="inlineStr"/>
+      <c r="B8" s="10" t="inlineStr">
         <is>
           <t>Você já prestou algum PS de consultoria? Se sim, quais empresas e até que fase chegou? O que te fez avançar e o que te derrubou? Se ainda não, qual mês ou ciclo você tem como alvo e quais empresas?</t>
         </is>
       </c>
-      <c r="C8" s="10" t="inlineStr">
+      <c r="C8" s="11" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="D8" s="11" t="inlineStr">
+      <c r="D8" s="12" t="inlineStr">
         <is>
           <t>Diferencie quem já está no funil de quem ainda vai entrar.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="46" customHeight="1">
-      <c r="A9" s="12" t="inlineStr"/>
-      <c r="B9" s="13" t="inlineStr">
+      <c r="A9" s="13" t="inlineStr"/>
+      <c r="B9" s="14" t="inlineStr">
         <is>
           <t>Como estão hoje seus planos de estágio e summer? O que já rolou, quais prazos (formatura, elegibilidade) te limitam, e o que ainda falta destravar?</t>
         </is>
       </c>
-      <c r="C9" s="14" t="inlineStr">
+      <c r="C9" s="15" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="D9" s="15" t="inlineStr">
+      <c r="D9" s="16" t="inlineStr">
         <is>
           <t>Cheque elegibilidade de summer x ano de formatura antes de indicar vaga.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="46" customHeight="1">
-      <c r="A10" s="8" t="inlineStr"/>
-      <c r="B10" s="9" t="inlineStr">
+      <c r="A10" s="9" t="inlineStr"/>
+      <c r="B10" s="10" t="inlineStr">
         <is>
           <t>Qual é o seu objetivo com o clube?</t>
         </is>
       </c>
-      <c r="C10" s="10" t="inlineStr">
+      <c r="C10" s="11" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="D10" s="11" t="inlineStr">
+      <c r="D10" s="12" t="inlineStr">
         <is>
           <t>Se o objetivo não for consultoria, o acompanhamento muda.</t>
         </is>
       </c>
     </row>
     <row r="11" ht="46" customHeight="1">
-      <c r="A11" s="12" t="inlineStr"/>
-      <c r="B11" s="13" t="inlineStr">
+      <c r="A11" s="13" t="inlineStr"/>
+      <c r="B11" s="14" t="inlineStr">
         <is>
           <t>Horizonte de saída do clube (lembrar o aviso mínimo de um mês).</t>
         </is>
       </c>
-      <c r="C11" s="14" t="inlineStr">
+      <c r="C11" s="15" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="D11" s="15" t="inlineStr">
+      <c r="D11" s="16" t="inlineStr">
         <is>
           <t>Alimenta o planejamento de sucessão da área.</t>
         </is>
@@ -912,93 +920,93 @@
           <t>1. COMO ESTÁ SENDO ESTAR AQUI</t>
         </is>
       </c>
-      <c r="B12" s="1" t="n"/>
-      <c r="C12" s="1" t="n"/>
-      <c r="D12" s="1" t="n"/>
+      <c r="B12" s="8" t="n"/>
+      <c r="C12" s="8" t="n"/>
+      <c r="D12" s="8" t="n"/>
     </row>
     <row r="13" ht="46" customHeight="1">
-      <c r="A13" s="8" t="inlineStr">
+      <c r="A13" s="9" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B13" s="9" t="inlineStr">
+      <c r="B13" s="10" t="inlineStr">
         <is>
           <t>Se você tivesse que descrever sua área para um candidato do próximo PS, o que você venderia com orgulho e o que você avisaria antes que ele entrasse?</t>
         </is>
       </c>
-      <c r="C13" s="10" t="inlineStr">
+      <c r="C13" s="11" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="D13" s="11" t="inlineStr">
+      <c r="D13" s="12" t="inlineStr">
         <is>
           <t>O “aviso” é o ouro: repetido por 3 pessoas, o problema é do processo, não da pessoa.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="46" customHeight="1">
-      <c r="A14" s="12" t="inlineStr">
+      <c r="A14" s="13" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B14" s="13" t="inlineStr">
+      <c r="B14" s="14" t="inlineStr">
         <is>
           <t>Qual foi a coisa mais útil que o clube te entregou nos últimos dois meses, e qual foi a que mais te pareceu perda de tempo?</t>
         </is>
       </c>
-      <c r="C14" s="14" t="inlineStr">
+      <c r="C14" s="15" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="D14" s="15" t="inlineStr">
+      <c r="D14" s="16" t="inlineStr">
         <is>
           <t>Mede valor percebido; a “perda de tempo” aponta o que cortar.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="46" customHeight="1">
-      <c r="A15" s="8" t="inlineStr">
+      <c r="A15" s="9" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B15" s="9" t="inlineStr">
+      <c r="B15" s="10" t="inlineStr">
         <is>
           <t>Você está satisfeito com a sua área? O que ela faz bem, o que deixa a desejar, e o que precisaria acontecer para você pensar em trocar?</t>
         </is>
       </c>
-      <c r="C15" s="10" t="inlineStr">
+      <c r="C15" s="11" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="D15" s="11" t="inlineStr">
+      <c r="D15" s="12" t="inlineStr">
         <is>
           <t>Sinal precoce de churn interno / pedido de transferência.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="46" customHeight="1">
-      <c r="A16" s="12" t="inlineStr">
+      <c r="A16" s="13" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B16" s="13" t="inlineStr">
+      <c r="B16" s="14" t="inlineStr">
         <is>
           <t>Como você descreveria o clima da sua área hoje? Tem alguém que te puxa para cima e algo que costuma te desanimar?</t>
         </is>
       </c>
-      <c r="C16" s="14" t="inlineStr">
+      <c r="C16" s="15" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="D16" s="15" t="inlineStr">
+      <c r="D16" s="16" t="inlineStr">
         <is>
           <t>Clima e relações; sinaliza engajamento e atritos que a nota não mostra.</t>
         </is>
@@ -1010,93 +1018,93 @@
           <t>2. ENTREGA, CASES E PROJETOS</t>
         </is>
       </c>
-      <c r="B17" s="1" t="n"/>
-      <c r="C17" s="1" t="n"/>
-      <c r="D17" s="1" t="n"/>
+      <c r="B17" s="8" t="n"/>
+      <c r="C17" s="8" t="n"/>
+      <c r="D17" s="8" t="n"/>
     </row>
     <row r="18" ht="46" customHeight="1">
-      <c r="A18" s="8" t="inlineStr">
+      <c r="A18" s="9" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B18" s="9" t="inlineStr">
+      <c r="B18" s="10" t="inlineStr">
         <is>
           <t>Pensando nos projetos internos e externos rodando hoje, qual deles te deixa com a sensação de “eu faria isso diferente”? O que você mudaria?</t>
         </is>
       </c>
-      <c r="C18" s="10" t="inlineStr">
+      <c r="C18" s="11" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="D18" s="11" t="inlineStr">
+      <c r="D18" s="12" t="inlineStr">
         <is>
           <t>Revela senso crítico e apetite por dono de entrega.</t>
         </is>
       </c>
     </row>
     <row r="19" ht="46" customHeight="1">
-      <c r="A19" s="12" t="inlineStr">
+      <c r="A19" s="13" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="B19" s="13" t="inlineStr">
+      <c r="B19" s="14" t="inlineStr">
         <is>
           <t>Tem algum projeto, ou tipo de projeto, que você gostaria de assumir? O que te atrai nele e o que hoje te segura de topar?</t>
         </is>
       </c>
-      <c r="C19" s="14" t="inlineStr">
+      <c r="C19" s="15" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="D19" s="15" t="inlineStr">
+      <c r="D19" s="16" t="inlineStr">
         <is>
           <t>Se travar em “não sei”, ofereça 2 opções concretas e veja a reação.</t>
         </is>
       </c>
     </row>
     <row r="20" ht="46" customHeight="1">
-      <c r="A20" s="8" t="inlineStr">
+      <c r="A20" s="9" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B20" s="9" t="inlineStr">
+      <c r="B20" s="10" t="inlineStr">
         <is>
           <t>Qual foi a última entrega (case, análise, apresentação) que te deu orgulho, e qual te mostrou um buraco que você ainda precisa fechar?</t>
         </is>
       </c>
-      <c r="C20" s="10" t="inlineStr">
+      <c r="C20" s="11" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="D20" s="11" t="inlineStr">
+      <c r="D20" s="12" t="inlineStr">
         <is>
           <t>Puxe exemplo datado; auto-percepção de gap vale mais que elogio.</t>
         </is>
       </c>
     </row>
     <row r="21" ht="46" customHeight="1">
-      <c r="A21" s="12" t="inlineStr">
+      <c r="A21" s="13" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="B21" s="13" t="inlineStr">
+      <c r="B21" s="14" t="inlineStr">
         <is>
           <t>Se você pudesse ser dono de um projeto do zero no clube, que problema real você gostaria de resolver e por quê?</t>
         </is>
       </c>
-      <c r="C21" s="14" t="inlineStr">
+      <c r="C21" s="15" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="D21" s="15" t="inlineStr">
+      <c r="D21" s="16" t="inlineStr">
         <is>
           <t>Mede iniciativa e o tipo de problema que de fato motiva a pessoa.</t>
         </is>
@@ -1108,71 +1116,71 @@
           <t>3. PREPARAÇÃO PARA O MERCADO</t>
         </is>
       </c>
-      <c r="B22" s="1" t="n"/>
-      <c r="C22" s="1" t="n"/>
-      <c r="D22" s="1" t="n"/>
+      <c r="B22" s="8" t="n"/>
+      <c r="C22" s="8" t="n"/>
+      <c r="D22" s="8" t="n"/>
     </row>
     <row r="23" ht="46" customHeight="1">
-      <c r="A23" s="8" t="inlineStr">
+      <c r="A23" s="9" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="B23" s="9" t="inlineStr">
+      <c r="B23" s="10" t="inlineStr">
         <is>
           <t>Numa escala de 0 a 10, quão pronto você se sente hoje para um PS de MBB? O que explica o número não ser 10, e o que precisaria acontecer nos próximos 3 meses para subir 2 pontos?</t>
         </is>
       </c>
-      <c r="C23" s="10" t="inlineStr">
+      <c r="C23" s="11" t="inlineStr">
         <is>
           <t>F · NOTA</t>
         </is>
       </c>
-      <c r="D23" s="11" t="inlineStr">
+      <c r="D23" s="12" t="inlineStr">
         <is>
           <t>Vira nota na Ficha e no Registro. O valor está no “por quê”.</t>
         </is>
       </c>
     </row>
     <row r="24" ht="46" customHeight="1">
-      <c r="A24" s="12" t="inlineStr">
+      <c r="A24" s="13" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B24" s="13" t="inlineStr">
+      <c r="B24" s="14" t="inlineStr">
         <is>
           <t>O que você sabe fazer hoje que não sabia quando entrou? Me dá um exemplo concreto de quando isso apareceu, num case, num treino de GMAT ou numa apresentação.</t>
         </is>
       </c>
-      <c r="C24" s="14" t="inlineStr">
+      <c r="C24" s="15" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="D24" s="15" t="inlineStr">
+      <c r="D24" s="16" t="inlineStr">
         <is>
           <t>Exemplo concreto = aprendizado real; sem exemplo, é percepção vaga.</t>
         </is>
       </c>
     </row>
     <row r="25" ht="46" customHeight="1">
-      <c r="A25" s="8" t="inlineStr">
+      <c r="A25" s="9" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B25" s="9" t="inlineStr">
+      <c r="B25" s="10" t="inlineStr">
         <is>
           <t>Onde você está no GMAT / estruturação de case / fit hoje, e qual dessas frentes está mais atrasada para o seu alvo?</t>
         </is>
       </c>
-      <c r="C25" s="10" t="inlineStr">
+      <c r="C25" s="11" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="D25" s="11" t="inlineStr">
+      <c r="D25" s="12" t="inlineStr">
         <is>
           <t>Casa a autoavaliação com o alvo de PS declarado no cadastro.</t>
         </is>
@@ -1184,71 +1192,71 @@
           <t>4. FUTURO NO CLUBE E RESPONSABILIDADE</t>
         </is>
       </c>
-      <c r="B26" s="1" t="n"/>
-      <c r="C26" s="1" t="n"/>
-      <c r="D26" s="1" t="n"/>
+      <c r="B26" s="8" t="n"/>
+      <c r="C26" s="8" t="n"/>
+      <c r="D26" s="8" t="n"/>
     </row>
     <row r="27" ht="46" customHeight="1">
-      <c r="A27" s="12" t="inlineStr">
+      <c r="A27" s="13" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="B27" s="13" t="inlineStr">
+      <c r="B27" s="14" t="inlineStr">
         <is>
           <t>Quando você imagina seu último semestre no clube, o que precisa ter acontecido para você olhar para trás e sentir que valeu? Que tipo de responsabilidade caberia nisso?</t>
         </is>
       </c>
-      <c r="C27" s="14" t="inlineStr">
+      <c r="C27" s="15" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="D27" s="15" t="inlineStr">
+      <c r="D27" s="16" t="inlineStr">
         <is>
           <t>Liga motivação a entrega; base para combinar um próximo passo.</t>
         </is>
       </c>
     </row>
     <row r="28" ht="46" customHeight="1">
-      <c r="A28" s="8" t="inlineStr">
+      <c r="A28" s="9" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="B28" s="9" t="inlineStr">
+      <c r="B28" s="10" t="inlineStr">
         <is>
           <t>Numa escala de 0 a 10, qual a chance de você continuar no clube no próximo semestre? O que subiria esse número em dois pontos?</t>
         </is>
       </c>
-      <c r="C28" s="10" t="inlineStr">
+      <c r="C28" s="11" t="inlineStr">
         <is>
           <t>F · NOTA</t>
         </is>
       </c>
-      <c r="D28" s="11" t="inlineStr">
+      <c r="D28" s="12" t="inlineStr">
         <is>
           <t>Nota de retenção. 6 ou menos = conversa de retenção nesta semana.</t>
         </is>
       </c>
     </row>
     <row r="29" ht="46" customHeight="1">
-      <c r="A29" s="12" t="inlineStr">
+      <c r="A29" s="13" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="B29" s="13" t="inlineStr">
+      <c r="B29" s="14" t="inlineStr">
         <is>
           <t>Você pensa em assumir um cargo de diretoria? Qual, e o que hoje pesa a favor e contra (tempo, estágio, aulas)?</t>
         </is>
       </c>
-      <c r="C29" s="14" t="inlineStr">
+      <c r="C29" s="15" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="D29" s="15" t="inlineStr">
+      <c r="D29" s="16" t="inlineStr">
         <is>
           <t>Mapeia pipeline de liderança e conflitos de agenda.</t>
         </is>
@@ -1260,49 +1268,49 @@
           <t>5. FEEDBACK PARA A DIRETORIA</t>
         </is>
       </c>
-      <c r="B30" s="1" t="n"/>
-      <c r="C30" s="1" t="n"/>
-      <c r="D30" s="1" t="n"/>
+      <c r="B30" s="8" t="n"/>
+      <c r="C30" s="8" t="n"/>
+      <c r="D30" s="8" t="n"/>
     </row>
     <row r="31" ht="46" customHeight="1">
-      <c r="A31" s="8" t="inlineStr">
+      <c r="A31" s="9" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="B31" s="9" t="inlineStr">
+      <c r="B31" s="10" t="inlineStr">
         <is>
           <t>Se você fosse o diretor responsável por você na semana que vem, qual seria a primeira coisa que mudaria na forma como a sua área é conduzida?</t>
         </is>
       </c>
-      <c r="C31" s="10" t="inlineStr">
+      <c r="C31" s="11" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="D31" s="11" t="inlineStr">
+      <c r="D31" s="12" t="inlineStr">
         <is>
           <t>Feedback acionável e imediato sobre a condução.</t>
         </is>
       </c>
     </row>
     <row r="32" ht="46" customHeight="1">
-      <c r="A32" s="12" t="inlineStr">
+      <c r="A32" s="13" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="B32" s="13" t="inlineStr">
+      <c r="B32" s="14" t="inlineStr">
         <is>
           <t>O que você sente que a diretoria não está enxergando hoje, sobre você, sobre sua área ou sobre o clube, que faria diferença se a gente soubesse?</t>
         </is>
       </c>
-      <c r="C32" s="14" t="inlineStr">
+      <c r="C32" s="15" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="D32" s="15" t="inlineStr">
+      <c r="D32" s="16" t="inlineStr">
         <is>
           <t>Abre pontos cegos; ótima para fechar a conversa com escuta.</t>
         </is>
@@ -1342,7 +1350,7 @@
     <col width="20" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" ht="34" customHeight="1">
+    <row r="1" ht="46" customHeight="1">
       <c r="A1" s="1" t="n"/>
       <c r="B1" s="1" t="n"/>
       <c r="C1" s="1" t="n"/>
@@ -1375,52 +1383,52 @@
       <c r="F3" s="5" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="16" t="inlineStr">
+      <c r="A4" s="17" t="inlineStr">
         <is>
           <t>Membro</t>
         </is>
       </c>
-      <c r="B4" s="17" t="n"/>
-      <c r="C4" s="17" t="n"/>
-      <c r="D4" s="16" t="inlineStr">
+      <c r="B4" s="18" t="n"/>
+      <c r="C4" s="18" t="n"/>
+      <c r="D4" s="17" t="inlineStr">
         <is>
           <t>Curso</t>
         </is>
       </c>
-      <c r="E4" s="17" t="n"/>
-      <c r="F4" s="17" t="n"/>
+      <c r="E4" s="18" t="n"/>
+      <c r="F4" s="18" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="16" t="inlineStr">
+      <c r="A5" s="17" t="inlineStr">
         <is>
           <t>Área / diretoria</t>
         </is>
       </c>
-      <c r="B5" s="17" t="n"/>
-      <c r="C5" s="17" t="n"/>
-      <c r="D5" s="16" t="inlineStr">
+      <c r="B5" s="18" t="n"/>
+      <c r="C5" s="18" t="n"/>
+      <c r="D5" s="17" t="inlineStr">
         <is>
           <t>Data</t>
         </is>
       </c>
-      <c r="E5" s="17" t="n"/>
-      <c r="F5" s="17" t="n"/>
+      <c r="E5" s="18" t="n"/>
+      <c r="F5" s="18" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="16" t="inlineStr">
+      <c r="A6" s="17" t="inlineStr">
         <is>
           <t>Tempo de clube</t>
         </is>
       </c>
-      <c r="B6" s="17" t="n"/>
-      <c r="C6" s="17" t="n"/>
-      <c r="D6" s="16" t="inlineStr">
+      <c r="B6" s="18" t="n"/>
+      <c r="C6" s="18" t="n"/>
+      <c r="D6" s="17" t="inlineStr">
         <is>
           <t>Quem conduziu</t>
         </is>
       </c>
-      <c r="E6" s="17" t="n"/>
-      <c r="F6" s="17" t="n"/>
+      <c r="E6" s="18" t="n"/>
+      <c r="F6" s="18" t="n"/>
     </row>
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="7" t="inlineStr">
@@ -1428,95 +1436,95 @@
           <t>CADASTRO RÁPIDO (preencher na 1ª conversa, revisar nas seguintes)</t>
         </is>
       </c>
-      <c r="B8" s="1" t="n"/>
-      <c r="C8" s="1" t="n"/>
-      <c r="D8" s="1" t="n"/>
-      <c r="E8" s="1" t="n"/>
-      <c r="F8" s="1" t="n"/>
+      <c r="B8" s="8" t="n"/>
+      <c r="C8" s="8" t="n"/>
+      <c r="D8" s="8" t="n"/>
+      <c r="E8" s="8" t="n"/>
+      <c r="F8" s="8" t="n"/>
     </row>
     <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="18" t="inlineStr">
+      <c r="A9" s="19" t="inlineStr">
         <is>
           <t>Já prestou PS? Quais e até que fase?</t>
         </is>
       </c>
-      <c r="B9" s="19" t="n"/>
-      <c r="C9" s="19" t="n"/>
-      <c r="D9" s="19" t="n"/>
-      <c r="E9" s="19" t="n"/>
-      <c r="F9" s="19" t="n"/>
+      <c r="B9" s="20" t="n"/>
+      <c r="C9" s="20" t="n"/>
+      <c r="D9" s="20" t="n"/>
+      <c r="E9" s="20" t="n"/>
+      <c r="F9" s="20" t="n"/>
     </row>
     <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="18" t="inlineStr">
+      <c r="A10" s="19" t="inlineStr">
         <is>
           <t>Se ainda não: alvo (ciclo / empresas)</t>
         </is>
       </c>
-      <c r="B10" s="19" t="n"/>
-      <c r="C10" s="19" t="n"/>
-      <c r="D10" s="19" t="n"/>
-      <c r="E10" s="19" t="n"/>
-      <c r="F10" s="19" t="n"/>
+      <c r="B10" s="20" t="n"/>
+      <c r="C10" s="20" t="n"/>
+      <c r="D10" s="20" t="n"/>
+      <c r="E10" s="20" t="n"/>
+      <c r="F10" s="20" t="n"/>
     </row>
     <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="18" t="inlineStr">
+      <c r="A11" s="19" t="inlineStr">
         <is>
           <t>Estágio (onde já estagia / quando pretende começar)</t>
         </is>
       </c>
-      <c r="B11" s="19" t="n"/>
-      <c r="C11" s="19" t="n"/>
-      <c r="D11" s="19" t="n"/>
-      <c r="E11" s="19" t="n"/>
-      <c r="F11" s="19" t="n"/>
+      <c r="B11" s="20" t="n"/>
+      <c r="C11" s="20" t="n"/>
+      <c r="D11" s="20" t="n"/>
+      <c r="E11" s="20" t="n"/>
+      <c r="F11" s="20" t="n"/>
     </row>
     <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="18" t="inlineStr">
+      <c r="A12" s="19" t="inlineStr">
         <is>
           <t>Summer (qual / formatura ou elegibilidade limita?)</t>
         </is>
       </c>
-      <c r="B12" s="19" t="n"/>
-      <c r="C12" s="19" t="n"/>
-      <c r="D12" s="19" t="n"/>
-      <c r="E12" s="19" t="n"/>
-      <c r="F12" s="19" t="n"/>
+      <c r="B12" s="20" t="n"/>
+      <c r="C12" s="20" t="n"/>
+      <c r="D12" s="20" t="n"/>
+      <c r="E12" s="20" t="n"/>
+      <c r="F12" s="20" t="n"/>
     </row>
     <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="18" t="inlineStr">
+      <c r="A13" s="19" t="inlineStr">
         <is>
           <t>Objetivo com o clube</t>
         </is>
       </c>
-      <c r="B13" s="19" t="n"/>
-      <c r="C13" s="19" t="n"/>
-      <c r="D13" s="19" t="n"/>
-      <c r="E13" s="19" t="n"/>
-      <c r="F13" s="19" t="n"/>
+      <c r="B13" s="20" t="n"/>
+      <c r="C13" s="20" t="n"/>
+      <c r="D13" s="20" t="n"/>
+      <c r="E13" s="20" t="n"/>
+      <c r="F13" s="20" t="n"/>
     </row>
     <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="18" t="inlineStr">
+      <c r="A14" s="19" t="inlineStr">
         <is>
           <t>Interesse em cargo de diretoria (qual?)</t>
         </is>
       </c>
-      <c r="B14" s="19" t="n"/>
-      <c r="C14" s="19" t="n"/>
-      <c r="D14" s="19" t="n"/>
-      <c r="E14" s="19" t="n"/>
-      <c r="F14" s="19" t="n"/>
+      <c r="B14" s="20" t="n"/>
+      <c r="C14" s="20" t="n"/>
+      <c r="D14" s="20" t="n"/>
+      <c r="E14" s="20" t="n"/>
+      <c r="F14" s="20" t="n"/>
     </row>
     <row r="15" ht="30" customHeight="1">
-      <c r="A15" s="18" t="inlineStr">
+      <c r="A15" s="19" t="inlineStr">
         <is>
           <t>Horizonte de saída (aviso mínimo de 1 mês)</t>
         </is>
       </c>
-      <c r="B15" s="19" t="n"/>
-      <c r="C15" s="19" t="n"/>
-      <c r="D15" s="19" t="n"/>
-      <c r="E15" s="19" t="n"/>
-      <c r="F15" s="19" t="n"/>
+      <c r="B15" s="20" t="n"/>
+      <c r="C15" s="20" t="n"/>
+      <c r="D15" s="20" t="n"/>
+      <c r="E15" s="20" t="n"/>
+      <c r="F15" s="20" t="n"/>
     </row>
     <row r="17" ht="20" customHeight="1">
       <c r="A17" s="7" t="inlineStr">
@@ -1524,179 +1532,179 @@
           <t>CONVERSA — PERGUNTAS FIXAS</t>
         </is>
       </c>
-      <c r="B17" s="1" t="n"/>
-      <c r="C17" s="1" t="n"/>
-      <c r="D17" s="1" t="n"/>
-      <c r="E17" s="1" t="n"/>
-      <c r="F17" s="1" t="n"/>
+      <c r="B17" s="8" t="n"/>
+      <c r="C17" s="8" t="n"/>
+      <c r="D17" s="8" t="n"/>
+      <c r="E17" s="8" t="n"/>
+      <c r="F17" s="8" t="n"/>
     </row>
     <row r="18" ht="34" customHeight="1">
-      <c r="A18" s="20" t="inlineStr">
+      <c r="A18" s="21" t="inlineStr">
         <is>
           <t>1. Descrevendo sua área para um candidato do próximo PS: o que você venderia com orgulho e o que avisaria antes que ele entrasse?</t>
         </is>
       </c>
-      <c r="B18" s="21" t="n"/>
-      <c r="C18" s="21" t="n"/>
-      <c r="D18" s="21" t="n"/>
-      <c r="E18" s="21" t="n"/>
-      <c r="F18" s="21" t="n"/>
+      <c r="B18" s="22" t="n"/>
+      <c r="C18" s="22" t="n"/>
+      <c r="D18" s="22" t="n"/>
+      <c r="E18" s="22" t="n"/>
+      <c r="F18" s="22" t="n"/>
     </row>
     <row r="19" ht="18" customHeight="1">
-      <c r="A19" s="19" t="n"/>
-      <c r="B19" s="19" t="n"/>
-      <c r="C19" s="19" t="n"/>
-      <c r="D19" s="19" t="n"/>
-      <c r="E19" s="19" t="n"/>
-      <c r="F19" s="19" t="n"/>
+      <c r="A19" s="20" t="n"/>
+      <c r="B19" s="20" t="n"/>
+      <c r="C19" s="20" t="n"/>
+      <c r="D19" s="20" t="n"/>
+      <c r="E19" s="20" t="n"/>
+      <c r="F19" s="20" t="n"/>
     </row>
     <row r="20" ht="18" customHeight="1">
-      <c r="A20" s="19" t="n"/>
-      <c r="B20" s="19" t="n"/>
-      <c r="C20" s="19" t="n"/>
-      <c r="D20" s="19" t="n"/>
-      <c r="E20" s="19" t="n"/>
-      <c r="F20" s="19" t="n"/>
+      <c r="A20" s="20" t="n"/>
+      <c r="B20" s="20" t="n"/>
+      <c r="C20" s="20" t="n"/>
+      <c r="D20" s="20" t="n"/>
+      <c r="E20" s="20" t="n"/>
+      <c r="F20" s="20" t="n"/>
     </row>
     <row r="21" ht="34" customHeight="1">
-      <c r="A21" s="20" t="inlineStr">
+      <c r="A21" s="21" t="inlineStr">
         <is>
           <t>2. A coisa mais útil que o clube te entregou nos últimos dois meses, e a que mais te pareceu perda de tempo?</t>
         </is>
       </c>
-      <c r="B21" s="21" t="n"/>
-      <c r="C21" s="21" t="n"/>
-      <c r="D21" s="21" t="n"/>
-      <c r="E21" s="21" t="n"/>
-      <c r="F21" s="21" t="n"/>
+      <c r="B21" s="22" t="n"/>
+      <c r="C21" s="22" t="n"/>
+      <c r="D21" s="22" t="n"/>
+      <c r="E21" s="22" t="n"/>
+      <c r="F21" s="22" t="n"/>
     </row>
     <row r="22" ht="18" customHeight="1">
-      <c r="A22" s="19" t="n"/>
-      <c r="B22" s="19" t="n"/>
-      <c r="C22" s="19" t="n"/>
-      <c r="D22" s="19" t="n"/>
-      <c r="E22" s="19" t="n"/>
-      <c r="F22" s="19" t="n"/>
+      <c r="A22" s="20" t="n"/>
+      <c r="B22" s="20" t="n"/>
+      <c r="C22" s="20" t="n"/>
+      <c r="D22" s="20" t="n"/>
+      <c r="E22" s="20" t="n"/>
+      <c r="F22" s="20" t="n"/>
     </row>
     <row r="23" ht="18" customHeight="1">
-      <c r="A23" s="19" t="n"/>
-      <c r="B23" s="19" t="n"/>
-      <c r="C23" s="19" t="n"/>
-      <c r="D23" s="19" t="n"/>
-      <c r="E23" s="19" t="n"/>
-      <c r="F23" s="19" t="n"/>
+      <c r="A23" s="20" t="n"/>
+      <c r="B23" s="20" t="n"/>
+      <c r="C23" s="20" t="n"/>
+      <c r="D23" s="20" t="n"/>
+      <c r="E23" s="20" t="n"/>
+      <c r="F23" s="20" t="n"/>
     </row>
     <row r="24" ht="34" customHeight="1">
-      <c r="A24" s="20" t="inlineStr">
+      <c r="A24" s="21" t="inlineStr">
         <is>
           <t>5. Dos projetos internos e externos de hoje, qual te deixa com a sensação de “eu faria diferente”? O que mudaria?</t>
         </is>
       </c>
-      <c r="B24" s="21" t="n"/>
-      <c r="C24" s="21" t="n"/>
-      <c r="D24" s="21" t="n"/>
-      <c r="E24" s="21" t="n"/>
-      <c r="F24" s="21" t="n"/>
+      <c r="B24" s="22" t="n"/>
+      <c r="C24" s="22" t="n"/>
+      <c r="D24" s="22" t="n"/>
+      <c r="E24" s="22" t="n"/>
+      <c r="F24" s="22" t="n"/>
     </row>
     <row r="25" ht="18" customHeight="1">
-      <c r="A25" s="19" t="n"/>
-      <c r="B25" s="19" t="n"/>
-      <c r="C25" s="19" t="n"/>
-      <c r="D25" s="19" t="n"/>
-      <c r="E25" s="19" t="n"/>
-      <c r="F25" s="19" t="n"/>
+      <c r="A25" s="20" t="n"/>
+      <c r="B25" s="20" t="n"/>
+      <c r="C25" s="20" t="n"/>
+      <c r="D25" s="20" t="n"/>
+      <c r="E25" s="20" t="n"/>
+      <c r="F25" s="20" t="n"/>
     </row>
     <row r="26" ht="18" customHeight="1">
-      <c r="A26" s="19" t="n"/>
-      <c r="B26" s="19" t="n"/>
-      <c r="C26" s="19" t="n"/>
-      <c r="D26" s="19" t="n"/>
-      <c r="E26" s="19" t="n"/>
-      <c r="F26" s="19" t="n"/>
+      <c r="A26" s="20" t="n"/>
+      <c r="B26" s="20" t="n"/>
+      <c r="C26" s="20" t="n"/>
+      <c r="D26" s="20" t="n"/>
+      <c r="E26" s="20" t="n"/>
+      <c r="F26" s="20" t="n"/>
     </row>
     <row r="27" ht="34" customHeight="1">
-      <c r="A27" s="20" t="inlineStr">
+      <c r="A27" s="21" t="inlineStr">
         <is>
           <t>10. O que você sabe fazer hoje que não sabia quando entrou? Me dá um exemplo concreto de quando isso apareceu.</t>
         </is>
       </c>
-      <c r="B27" s="21" t="n"/>
-      <c r="C27" s="21" t="n"/>
-      <c r="D27" s="21" t="n"/>
-      <c r="E27" s="21" t="n"/>
-      <c r="F27" s="21" t="n"/>
+      <c r="B27" s="22" t="n"/>
+      <c r="C27" s="22" t="n"/>
+      <c r="D27" s="22" t="n"/>
+      <c r="E27" s="22" t="n"/>
+      <c r="F27" s="22" t="n"/>
     </row>
     <row r="28" ht="18" customHeight="1">
-      <c r="A28" s="19" t="n"/>
-      <c r="B28" s="19" t="n"/>
-      <c r="C28" s="19" t="n"/>
-      <c r="D28" s="19" t="n"/>
-      <c r="E28" s="19" t="n"/>
-      <c r="F28" s="19" t="n"/>
+      <c r="A28" s="20" t="n"/>
+      <c r="B28" s="20" t="n"/>
+      <c r="C28" s="20" t="n"/>
+      <c r="D28" s="20" t="n"/>
+      <c r="E28" s="20" t="n"/>
+      <c r="F28" s="20" t="n"/>
     </row>
     <row r="29" ht="18" customHeight="1">
-      <c r="A29" s="19" t="n"/>
-      <c r="B29" s="19" t="n"/>
-      <c r="C29" s="19" t="n"/>
-      <c r="D29" s="19" t="n"/>
-      <c r="E29" s="19" t="n"/>
-      <c r="F29" s="19" t="n"/>
+      <c r="A29" s="20" t="n"/>
+      <c r="B29" s="20" t="n"/>
+      <c r="C29" s="20" t="n"/>
+      <c r="D29" s="20" t="n"/>
+      <c r="E29" s="20" t="n"/>
+      <c r="F29" s="20" t="n"/>
     </row>
     <row r="30" ht="34" customHeight="1">
-      <c r="A30" s="20" t="inlineStr">
+      <c r="A30" s="21" t="inlineStr">
         <is>
           <t>12. Imaginando seu último semestre no clube: o que precisa ter acontecido para sentir que valeu? Que responsabilidade caberia nisso?</t>
         </is>
       </c>
-      <c r="B30" s="21" t="n"/>
-      <c r="C30" s="21" t="n"/>
-      <c r="D30" s="21" t="n"/>
-      <c r="E30" s="21" t="n"/>
-      <c r="F30" s="21" t="n"/>
+      <c r="B30" s="22" t="n"/>
+      <c r="C30" s="22" t="n"/>
+      <c r="D30" s="22" t="n"/>
+      <c r="E30" s="22" t="n"/>
+      <c r="F30" s="22" t="n"/>
     </row>
     <row r="31" ht="18" customHeight="1">
-      <c r="A31" s="19" t="n"/>
-      <c r="B31" s="19" t="n"/>
-      <c r="C31" s="19" t="n"/>
-      <c r="D31" s="19" t="n"/>
-      <c r="E31" s="19" t="n"/>
-      <c r="F31" s="19" t="n"/>
+      <c r="A31" s="20" t="n"/>
+      <c r="B31" s="20" t="n"/>
+      <c r="C31" s="20" t="n"/>
+      <c r="D31" s="20" t="n"/>
+      <c r="E31" s="20" t="n"/>
+      <c r="F31" s="20" t="n"/>
     </row>
     <row r="32" ht="18" customHeight="1">
-      <c r="A32" s="19" t="n"/>
-      <c r="B32" s="19" t="n"/>
-      <c r="C32" s="19" t="n"/>
-      <c r="D32" s="19" t="n"/>
-      <c r="E32" s="19" t="n"/>
-      <c r="F32" s="19" t="n"/>
+      <c r="A32" s="20" t="n"/>
+      <c r="B32" s="20" t="n"/>
+      <c r="C32" s="20" t="n"/>
+      <c r="D32" s="20" t="n"/>
+      <c r="E32" s="20" t="n"/>
+      <c r="F32" s="20" t="n"/>
     </row>
     <row r="33" ht="34" customHeight="1">
-      <c r="A33" s="20" t="inlineStr">
+      <c r="A33" s="21" t="inlineStr">
         <is>
           <t>15. Se você fosse o diretor responsável por você na semana que vem, qual a primeira coisa que mudaria na condução da área?</t>
         </is>
       </c>
-      <c r="B33" s="21" t="n"/>
-      <c r="C33" s="21" t="n"/>
-      <c r="D33" s="21" t="n"/>
-      <c r="E33" s="21" t="n"/>
-      <c r="F33" s="21" t="n"/>
+      <c r="B33" s="22" t="n"/>
+      <c r="C33" s="22" t="n"/>
+      <c r="D33" s="22" t="n"/>
+      <c r="E33" s="22" t="n"/>
+      <c r="F33" s="22" t="n"/>
     </row>
     <row r="34" ht="18" customHeight="1">
-      <c r="A34" s="19" t="n"/>
-      <c r="B34" s="19" t="n"/>
-      <c r="C34" s="19" t="n"/>
-      <c r="D34" s="19" t="n"/>
-      <c r="E34" s="19" t="n"/>
-      <c r="F34" s="19" t="n"/>
+      <c r="A34" s="20" t="n"/>
+      <c r="B34" s="20" t="n"/>
+      <c r="C34" s="20" t="n"/>
+      <c r="D34" s="20" t="n"/>
+      <c r="E34" s="20" t="n"/>
+      <c r="F34" s="20" t="n"/>
     </row>
     <row r="35" ht="18" customHeight="1">
-      <c r="A35" s="19" t="n"/>
-      <c r="B35" s="19" t="n"/>
-      <c r="C35" s="19" t="n"/>
-      <c r="D35" s="19" t="n"/>
-      <c r="E35" s="19" t="n"/>
-      <c r="F35" s="19" t="n"/>
+      <c r="A35" s="20" t="n"/>
+      <c r="B35" s="20" t="n"/>
+      <c r="C35" s="20" t="n"/>
+      <c r="D35" s="20" t="n"/>
+      <c r="E35" s="20" t="n"/>
+      <c r="F35" s="20" t="n"/>
     </row>
     <row r="37" ht="20" customHeight="1">
       <c r="A37" s="7" t="inlineStr">
@@ -1704,43 +1712,43 @@
           <t>AS DUAS NOTAS DA CONVERSA (0 a 10)</t>
         </is>
       </c>
-      <c r="B37" s="1" t="n"/>
-      <c r="C37" s="1" t="n"/>
-      <c r="D37" s="1" t="n"/>
-      <c r="E37" s="1" t="n"/>
-      <c r="F37" s="1" t="n"/>
+      <c r="B37" s="8" t="n"/>
+      <c r="C37" s="8" t="n"/>
+      <c r="D37" s="8" t="n"/>
+      <c r="E37" s="8" t="n"/>
+      <c r="F37" s="8" t="n"/>
     </row>
     <row r="38" ht="30" customHeight="1">
-      <c r="A38" s="22" t="inlineStr">
+      <c r="A38" s="23" t="inlineStr">
         <is>
           <t>Quão pronto se sente para um PS de MBB (pergunta 9)</t>
         </is>
       </c>
-      <c r="B38" s="23" t="n"/>
-      <c r="C38" s="9" t="inlineStr">
+      <c r="B38" s="24" t="n"/>
+      <c r="C38" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">Por quê: </t>
         </is>
       </c>
-      <c r="D38" s="19" t="n"/>
-      <c r="E38" s="19" t="n"/>
-      <c r="F38" s="19" t="n"/>
+      <c r="D38" s="20" t="n"/>
+      <c r="E38" s="20" t="n"/>
+      <c r="F38" s="20" t="n"/>
     </row>
     <row r="39" ht="30" customHeight="1">
-      <c r="A39" s="22" t="inlineStr">
+      <c r="A39" s="23" t="inlineStr">
         <is>
           <t>Chance de continuar no clube no próximo semestre (pergunta 13)</t>
         </is>
       </c>
-      <c r="B39" s="23" t="n"/>
-      <c r="C39" s="9" t="inlineStr">
+      <c r="B39" s="24" t="n"/>
+      <c r="C39" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">Por quê: </t>
         </is>
       </c>
-      <c r="D39" s="19" t="n"/>
-      <c r="E39" s="19" t="n"/>
-      <c r="F39" s="19" t="n"/>
+      <c r="D39" s="20" t="n"/>
+      <c r="E39" s="20" t="n"/>
+      <c r="F39" s="20" t="n"/>
     </row>
     <row r="41" ht="20" customHeight="1">
       <c r="A41" s="7" t="inlineStr">
@@ -1748,71 +1756,71 @@
           <t>PERGUNTAS ROTATIVAS QUE ESCOLHI HOJE (2 ou 3, do banco)</t>
         </is>
       </c>
-      <c r="B41" s="1" t="n"/>
-      <c r="C41" s="1" t="n"/>
-      <c r="D41" s="1" t="n"/>
-      <c r="E41" s="1" t="n"/>
-      <c r="F41" s="1" t="n"/>
+      <c r="B41" s="8" t="n"/>
+      <c r="C41" s="8" t="n"/>
+      <c r="D41" s="8" t="n"/>
+      <c r="E41" s="8" t="n"/>
+      <c r="F41" s="8" t="n"/>
     </row>
     <row r="42" ht="34" customHeight="1">
-      <c r="A42" s="20" t="inlineStr"/>
-      <c r="B42" s="21" t="n"/>
-      <c r="C42" s="21" t="n"/>
-      <c r="D42" s="21" t="n"/>
-      <c r="E42" s="21" t="n"/>
-      <c r="F42" s="21" t="n"/>
+      <c r="A42" s="21" t="inlineStr"/>
+      <c r="B42" s="22" t="n"/>
+      <c r="C42" s="22" t="n"/>
+      <c r="D42" s="22" t="n"/>
+      <c r="E42" s="22" t="n"/>
+      <c r="F42" s="22" t="n"/>
     </row>
     <row r="43" ht="18" customHeight="1">
-      <c r="A43" s="19" t="n"/>
-      <c r="B43" s="19" t="n"/>
-      <c r="C43" s="19" t="n"/>
-      <c r="D43" s="19" t="n"/>
-      <c r="E43" s="19" t="n"/>
-      <c r="F43" s="19" t="n"/>
+      <c r="A43" s="20" t="n"/>
+      <c r="B43" s="20" t="n"/>
+      <c r="C43" s="20" t="n"/>
+      <c r="D43" s="20" t="n"/>
+      <c r="E43" s="20" t="n"/>
+      <c r="F43" s="20" t="n"/>
     </row>
     <row r="44" ht="34" customHeight="1">
-      <c r="A44" s="20" t="inlineStr"/>
-      <c r="B44" s="21" t="n"/>
-      <c r="C44" s="21" t="n"/>
-      <c r="D44" s="21" t="n"/>
-      <c r="E44" s="21" t="n"/>
-      <c r="F44" s="21" t="n"/>
+      <c r="A44" s="21" t="inlineStr"/>
+      <c r="B44" s="22" t="n"/>
+      <c r="C44" s="22" t="n"/>
+      <c r="D44" s="22" t="n"/>
+      <c r="E44" s="22" t="n"/>
+      <c r="F44" s="22" t="n"/>
     </row>
     <row r="45" ht="18" customHeight="1">
-      <c r="A45" s="19" t="n"/>
-      <c r="B45" s="19" t="n"/>
-      <c r="C45" s="19" t="n"/>
-      <c r="D45" s="19" t="n"/>
-      <c r="E45" s="19" t="n"/>
-      <c r="F45" s="19" t="n"/>
+      <c r="A45" s="20" t="n"/>
+      <c r="B45" s="20" t="n"/>
+      <c r="C45" s="20" t="n"/>
+      <c r="D45" s="20" t="n"/>
+      <c r="E45" s="20" t="n"/>
+      <c r="F45" s="20" t="n"/>
     </row>
     <row r="46" ht="34" customHeight="1">
-      <c r="A46" s="20" t="inlineStr"/>
-      <c r="B46" s="21" t="n"/>
-      <c r="C46" s="21" t="n"/>
-      <c r="D46" s="21" t="n"/>
-      <c r="E46" s="21" t="n"/>
-      <c r="F46" s="21" t="n"/>
+      <c r="A46" s="21" t="inlineStr"/>
+      <c r="B46" s="22" t="n"/>
+      <c r="C46" s="22" t="n"/>
+      <c r="D46" s="22" t="n"/>
+      <c r="E46" s="22" t="n"/>
+      <c r="F46" s="22" t="n"/>
     </row>
     <row r="47" ht="18" customHeight="1">
-      <c r="A47" s="19" t="n"/>
-      <c r="B47" s="19" t="n"/>
-      <c r="C47" s="19" t="n"/>
-      <c r="D47" s="19" t="n"/>
-      <c r="E47" s="19" t="n"/>
-      <c r="F47" s="19" t="n"/>
+      <c r="A47" s="20" t="n"/>
+      <c r="B47" s="20" t="n"/>
+      <c r="C47" s="20" t="n"/>
+      <c r="D47" s="20" t="n"/>
+      <c r="E47" s="20" t="n"/>
+      <c r="F47" s="20" t="n"/>
     </row>
     <row r="49" ht="32" customHeight="1">
-      <c r="A49" s="24" t="inlineStr">
+      <c r="A49" s="25" t="inlineStr">
         <is>
           <t>Regra de ouro: nota de continuar 6 ou menos vira conversa de retenção nesta semana. Se a resposta vier genérica, pergunte “me dá um exemplo concreto” antes de seguir.</t>
         </is>
       </c>
-      <c r="B49" s="25" t="n"/>
-      <c r="C49" s="25" t="n"/>
-      <c r="D49" s="25" t="n"/>
-      <c r="E49" s="25" t="n"/>
-      <c r="F49" s="25" t="n"/>
+      <c r="B49" s="26" t="n"/>
+      <c r="C49" s="26" t="n"/>
+      <c r="D49" s="26" t="n"/>
+      <c r="E49" s="26" t="n"/>
+      <c r="F49" s="26" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="47">
@@ -1906,7 +1914,7 @@
     <col width="14" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
-    <row r="1" ht="34" customHeight="1">
+    <row r="1" ht="46" customHeight="1">
       <c r="A1" s="1" t="n"/>
       <c r="B1" s="1" t="n"/>
       <c r="C1" s="1" t="n"/>
@@ -1975,104 +1983,104 @@
       <c r="R3" s="5" t="n"/>
     </row>
     <row r="4" ht="40" customHeight="1">
-      <c r="A4" s="26" t="inlineStr">
+      <c r="A4" s="27" t="inlineStr">
         <is>
           <t>Membro</t>
         </is>
       </c>
-      <c r="B4" s="26" t="inlineStr">
+      <c r="B4" s="27" t="inlineStr">
         <is>
           <t>Data</t>
         </is>
       </c>
-      <c r="C4" s="26" t="inlineStr">
+      <c r="C4" s="27" t="inlineStr">
         <is>
           <t>Curso</t>
         </is>
       </c>
-      <c r="D4" s="26" t="inlineStr">
+      <c r="D4" s="27" t="inlineStr">
         <is>
           <t>Está entregando
 os cases?</t>
         </is>
       </c>
-      <c r="E4" s="26" t="inlineStr">
+      <c r="E4" s="27" t="inlineStr">
         <is>
           <t>Pronto p/
 PS (0-10)</t>
         </is>
       </c>
-      <c r="F4" s="26" t="inlineStr">
+      <c r="F4" s="27" t="inlineStr">
         <is>
           <t>Continuar no
 clube (0-10)</t>
         </is>
       </c>
-      <c r="G4" s="26" t="inlineStr">
+      <c r="G4" s="27" t="inlineStr">
         <is>
           <t>Alvo de PS
 (empresa / ciclo)</t>
         </is>
       </c>
-      <c r="H4" s="26" t="inlineStr">
+      <c r="H4" s="27" t="inlineStr">
         <is>
           <t>Estágio / Summer</t>
         </is>
       </c>
-      <c r="I4" s="26" t="inlineStr">
+      <c r="I4" s="27" t="inlineStr">
         <is>
           <t>Interesse em
 cargo</t>
         </is>
       </c>
-      <c r="J4" s="26" t="inlineStr">
+      <c r="J4" s="27" t="inlineStr">
         <is>
           <t>Satisfação com
 a área</t>
         </is>
       </c>
-      <c r="K4" s="26" t="inlineStr">
+      <c r="K4" s="27" t="inlineStr">
         <is>
           <t>Orgulho da área</t>
         </is>
       </c>
-      <c r="L4" s="26" t="inlineStr">
+      <c r="L4" s="27" t="inlineStr">
         <is>
           <t>Aviso que daria
 a um candidato</t>
         </is>
       </c>
-      <c r="M4" s="26" t="inlineStr">
+      <c r="M4" s="27" t="inlineStr">
         <is>
           <t>Mais útil nos
 2 meses</t>
         </is>
       </c>
-      <c r="N4" s="26" t="inlineStr">
+      <c r="N4" s="27" t="inlineStr">
         <is>
           <t>O que foi
 perda de tempo</t>
         </is>
       </c>
-      <c r="O4" s="26" t="inlineStr">
+      <c r="O4" s="27" t="inlineStr">
         <is>
           <t>O que mudaria na
 condução da área</t>
         </is>
       </c>
-      <c r="P4" s="26" t="inlineStr">
+      <c r="P4" s="27" t="inlineStr">
         <is>
           <t>Responsabilidade
 que quer assumir</t>
         </is>
       </c>
-      <c r="Q4" s="26" t="inlineStr">
+      <c r="Q4" s="27" t="inlineStr">
         <is>
           <t>Próximo passo
 combinado</t>
         </is>
       </c>
-      <c r="R4" s="26" t="inlineStr">
+      <c r="R4" s="27" t="inlineStr">
         <is>
           <t>Status do
 combinado</t>
@@ -2080,1404 +2088,1404 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="27" t="n"/>
-      <c r="B5" s="27" t="n"/>
-      <c r="C5" s="27" t="n"/>
-      <c r="D5" s="27" t="n"/>
-      <c r="E5" s="27" t="n"/>
-      <c r="F5" s="27" t="n"/>
-      <c r="G5" s="27" t="n"/>
-      <c r="H5" s="27" t="n"/>
-      <c r="I5" s="27" t="n"/>
-      <c r="J5" s="27" t="n"/>
-      <c r="K5" s="27" t="n"/>
-      <c r="L5" s="27" t="n"/>
-      <c r="M5" s="27" t="n"/>
-      <c r="N5" s="27" t="n"/>
-      <c r="O5" s="27" t="n"/>
-      <c r="P5" s="27" t="n"/>
-      <c r="Q5" s="27" t="n"/>
-      <c r="R5" s="27" t="n"/>
+      <c r="A5" s="28" t="n"/>
+      <c r="B5" s="28" t="n"/>
+      <c r="C5" s="28" t="n"/>
+      <c r="D5" s="28" t="n"/>
+      <c r="E5" s="28" t="n"/>
+      <c r="F5" s="28" t="n"/>
+      <c r="G5" s="28" t="n"/>
+      <c r="H5" s="28" t="n"/>
+      <c r="I5" s="28" t="n"/>
+      <c r="J5" s="28" t="n"/>
+      <c r="K5" s="28" t="n"/>
+      <c r="L5" s="28" t="n"/>
+      <c r="M5" s="28" t="n"/>
+      <c r="N5" s="28" t="n"/>
+      <c r="O5" s="28" t="n"/>
+      <c r="P5" s="28" t="n"/>
+      <c r="Q5" s="28" t="n"/>
+      <c r="R5" s="28" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="28" t="n"/>
-      <c r="B6" s="28" t="n"/>
-      <c r="C6" s="28" t="n"/>
-      <c r="D6" s="28" t="n"/>
-      <c r="E6" s="28" t="n"/>
-      <c r="F6" s="28" t="n"/>
-      <c r="G6" s="28" t="n"/>
-      <c r="H6" s="28" t="n"/>
-      <c r="I6" s="28" t="n"/>
-      <c r="J6" s="28" t="n"/>
-      <c r="K6" s="28" t="n"/>
-      <c r="L6" s="28" t="n"/>
-      <c r="M6" s="28" t="n"/>
-      <c r="N6" s="28" t="n"/>
-      <c r="O6" s="28" t="n"/>
-      <c r="P6" s="28" t="n"/>
-      <c r="Q6" s="28" t="n"/>
-      <c r="R6" s="28" t="n"/>
+      <c r="A6" s="29" t="n"/>
+      <c r="B6" s="29" t="n"/>
+      <c r="C6" s="29" t="n"/>
+      <c r="D6" s="29" t="n"/>
+      <c r="E6" s="29" t="n"/>
+      <c r="F6" s="29" t="n"/>
+      <c r="G6" s="29" t="n"/>
+      <c r="H6" s="29" t="n"/>
+      <c r="I6" s="29" t="n"/>
+      <c r="J6" s="29" t="n"/>
+      <c r="K6" s="29" t="n"/>
+      <c r="L6" s="29" t="n"/>
+      <c r="M6" s="29" t="n"/>
+      <c r="N6" s="29" t="n"/>
+      <c r="O6" s="29" t="n"/>
+      <c r="P6" s="29" t="n"/>
+      <c r="Q6" s="29" t="n"/>
+      <c r="R6" s="29" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="27" t="n"/>
-      <c r="B7" s="27" t="n"/>
-      <c r="C7" s="27" t="n"/>
-      <c r="D7" s="27" t="n"/>
-      <c r="E7" s="27" t="n"/>
-      <c r="F7" s="27" t="n"/>
-      <c r="G7" s="27" t="n"/>
-      <c r="H7" s="27" t="n"/>
-      <c r="I7" s="27" t="n"/>
-      <c r="J7" s="27" t="n"/>
-      <c r="K7" s="27" t="n"/>
-      <c r="L7" s="27" t="n"/>
-      <c r="M7" s="27" t="n"/>
-      <c r="N7" s="27" t="n"/>
-      <c r="O7" s="27" t="n"/>
-      <c r="P7" s="27" t="n"/>
-      <c r="Q7" s="27" t="n"/>
-      <c r="R7" s="27" t="n"/>
+      <c r="A7" s="28" t="n"/>
+      <c r="B7" s="28" t="n"/>
+      <c r="C7" s="28" t="n"/>
+      <c r="D7" s="28" t="n"/>
+      <c r="E7" s="28" t="n"/>
+      <c r="F7" s="28" t="n"/>
+      <c r="G7" s="28" t="n"/>
+      <c r="H7" s="28" t="n"/>
+      <c r="I7" s="28" t="n"/>
+      <c r="J7" s="28" t="n"/>
+      <c r="K7" s="28" t="n"/>
+      <c r="L7" s="28" t="n"/>
+      <c r="M7" s="28" t="n"/>
+      <c r="N7" s="28" t="n"/>
+      <c r="O7" s="28" t="n"/>
+      <c r="P7" s="28" t="n"/>
+      <c r="Q7" s="28" t="n"/>
+      <c r="R7" s="28" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="28" t="n"/>
-      <c r="B8" s="28" t="n"/>
-      <c r="C8" s="28" t="n"/>
-      <c r="D8" s="28" t="n"/>
-      <c r="E8" s="28" t="n"/>
-      <c r="F8" s="28" t="n"/>
-      <c r="G8" s="28" t="n"/>
-      <c r="H8" s="28" t="n"/>
-      <c r="I8" s="28" t="n"/>
-      <c r="J8" s="28" t="n"/>
-      <c r="K8" s="28" t="n"/>
-      <c r="L8" s="28" t="n"/>
-      <c r="M8" s="28" t="n"/>
-      <c r="N8" s="28" t="n"/>
-      <c r="O8" s="28" t="n"/>
-      <c r="P8" s="28" t="n"/>
-      <c r="Q8" s="28" t="n"/>
-      <c r="R8" s="28" t="n"/>
+      <c r="A8" s="29" t="n"/>
+      <c r="B8" s="29" t="n"/>
+      <c r="C8" s="29" t="n"/>
+      <c r="D8" s="29" t="n"/>
+      <c r="E8" s="29" t="n"/>
+      <c r="F8" s="29" t="n"/>
+      <c r="G8" s="29" t="n"/>
+      <c r="H8" s="29" t="n"/>
+      <c r="I8" s="29" t="n"/>
+      <c r="J8" s="29" t="n"/>
+      <c r="K8" s="29" t="n"/>
+      <c r="L8" s="29" t="n"/>
+      <c r="M8" s="29" t="n"/>
+      <c r="N8" s="29" t="n"/>
+      <c r="O8" s="29" t="n"/>
+      <c r="P8" s="29" t="n"/>
+      <c r="Q8" s="29" t="n"/>
+      <c r="R8" s="29" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="27" t="n"/>
-      <c r="B9" s="27" t="n"/>
-      <c r="C9" s="27" t="n"/>
-      <c r="D9" s="27" t="n"/>
-      <c r="E9" s="27" t="n"/>
-      <c r="F9" s="27" t="n"/>
-      <c r="G9" s="27" t="n"/>
-      <c r="H9" s="27" t="n"/>
-      <c r="I9" s="27" t="n"/>
-      <c r="J9" s="27" t="n"/>
-      <c r="K9" s="27" t="n"/>
-      <c r="L9" s="27" t="n"/>
-      <c r="M9" s="27" t="n"/>
-      <c r="N9" s="27" t="n"/>
-      <c r="O9" s="27" t="n"/>
-      <c r="P9" s="27" t="n"/>
-      <c r="Q9" s="27" t="n"/>
-      <c r="R9" s="27" t="n"/>
+      <c r="A9" s="28" t="n"/>
+      <c r="B9" s="28" t="n"/>
+      <c r="C9" s="28" t="n"/>
+      <c r="D9" s="28" t="n"/>
+      <c r="E9" s="28" t="n"/>
+      <c r="F9" s="28" t="n"/>
+      <c r="G9" s="28" t="n"/>
+      <c r="H9" s="28" t="n"/>
+      <c r="I9" s="28" t="n"/>
+      <c r="J9" s="28" t="n"/>
+      <c r="K9" s="28" t="n"/>
+      <c r="L9" s="28" t="n"/>
+      <c r="M9" s="28" t="n"/>
+      <c r="N9" s="28" t="n"/>
+      <c r="O9" s="28" t="n"/>
+      <c r="P9" s="28" t="n"/>
+      <c r="Q9" s="28" t="n"/>
+      <c r="R9" s="28" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="28" t="n"/>
-      <c r="B10" s="28" t="n"/>
-      <c r="C10" s="28" t="n"/>
-      <c r="D10" s="28" t="n"/>
-      <c r="E10" s="28" t="n"/>
-      <c r="F10" s="28" t="n"/>
-      <c r="G10" s="28" t="n"/>
-      <c r="H10" s="28" t="n"/>
-      <c r="I10" s="28" t="n"/>
-      <c r="J10" s="28" t="n"/>
-      <c r="K10" s="28" t="n"/>
-      <c r="L10" s="28" t="n"/>
-      <c r="M10" s="28" t="n"/>
-      <c r="N10" s="28" t="n"/>
-      <c r="O10" s="28" t="n"/>
-      <c r="P10" s="28" t="n"/>
-      <c r="Q10" s="28" t="n"/>
-      <c r="R10" s="28" t="n"/>
+      <c r="A10" s="29" t="n"/>
+      <c r="B10" s="29" t="n"/>
+      <c r="C10" s="29" t="n"/>
+      <c r="D10" s="29" t="n"/>
+      <c r="E10" s="29" t="n"/>
+      <c r="F10" s="29" t="n"/>
+      <c r="G10" s="29" t="n"/>
+      <c r="H10" s="29" t="n"/>
+      <c r="I10" s="29" t="n"/>
+      <c r="J10" s="29" t="n"/>
+      <c r="K10" s="29" t="n"/>
+      <c r="L10" s="29" t="n"/>
+      <c r="M10" s="29" t="n"/>
+      <c r="N10" s="29" t="n"/>
+      <c r="O10" s="29" t="n"/>
+      <c r="P10" s="29" t="n"/>
+      <c r="Q10" s="29" t="n"/>
+      <c r="R10" s="29" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="27" t="n"/>
-      <c r="B11" s="27" t="n"/>
-      <c r="C11" s="27" t="n"/>
-      <c r="D11" s="27" t="n"/>
-      <c r="E11" s="27" t="n"/>
-      <c r="F11" s="27" t="n"/>
-      <c r="G11" s="27" t="n"/>
-      <c r="H11" s="27" t="n"/>
-      <c r="I11" s="27" t="n"/>
-      <c r="J11" s="27" t="n"/>
-      <c r="K11" s="27" t="n"/>
-      <c r="L11" s="27" t="n"/>
-      <c r="M11" s="27" t="n"/>
-      <c r="N11" s="27" t="n"/>
-      <c r="O11" s="27" t="n"/>
-      <c r="P11" s="27" t="n"/>
-      <c r="Q11" s="27" t="n"/>
-      <c r="R11" s="27" t="n"/>
+      <c r="A11" s="28" t="n"/>
+      <c r="B11" s="28" t="n"/>
+      <c r="C11" s="28" t="n"/>
+      <c r="D11" s="28" t="n"/>
+      <c r="E11" s="28" t="n"/>
+      <c r="F11" s="28" t="n"/>
+      <c r="G11" s="28" t="n"/>
+      <c r="H11" s="28" t="n"/>
+      <c r="I11" s="28" t="n"/>
+      <c r="J11" s="28" t="n"/>
+      <c r="K11" s="28" t="n"/>
+      <c r="L11" s="28" t="n"/>
+      <c r="M11" s="28" t="n"/>
+      <c r="N11" s="28" t="n"/>
+      <c r="O11" s="28" t="n"/>
+      <c r="P11" s="28" t="n"/>
+      <c r="Q11" s="28" t="n"/>
+      <c r="R11" s="28" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="28" t="n"/>
-      <c r="B12" s="28" t="n"/>
-      <c r="C12" s="28" t="n"/>
-      <c r="D12" s="28" t="n"/>
-      <c r="E12" s="28" t="n"/>
-      <c r="F12" s="28" t="n"/>
-      <c r="G12" s="28" t="n"/>
-      <c r="H12" s="28" t="n"/>
-      <c r="I12" s="28" t="n"/>
-      <c r="J12" s="28" t="n"/>
-      <c r="K12" s="28" t="n"/>
-      <c r="L12" s="28" t="n"/>
-      <c r="M12" s="28" t="n"/>
-      <c r="N12" s="28" t="n"/>
-      <c r="O12" s="28" t="n"/>
-      <c r="P12" s="28" t="n"/>
-      <c r="Q12" s="28" t="n"/>
-      <c r="R12" s="28" t="n"/>
+      <c r="A12" s="29" t="n"/>
+      <c r="B12" s="29" t="n"/>
+      <c r="C12" s="29" t="n"/>
+      <c r="D12" s="29" t="n"/>
+      <c r="E12" s="29" t="n"/>
+      <c r="F12" s="29" t="n"/>
+      <c r="G12" s="29" t="n"/>
+      <c r="H12" s="29" t="n"/>
+      <c r="I12" s="29" t="n"/>
+      <c r="J12" s="29" t="n"/>
+      <c r="K12" s="29" t="n"/>
+      <c r="L12" s="29" t="n"/>
+      <c r="M12" s="29" t="n"/>
+      <c r="N12" s="29" t="n"/>
+      <c r="O12" s="29" t="n"/>
+      <c r="P12" s="29" t="n"/>
+      <c r="Q12" s="29" t="n"/>
+      <c r="R12" s="29" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="27" t="n"/>
-      <c r="B13" s="27" t="n"/>
-      <c r="C13" s="27" t="n"/>
-      <c r="D13" s="27" t="n"/>
-      <c r="E13" s="27" t="n"/>
-      <c r="F13" s="27" t="n"/>
-      <c r="G13" s="27" t="n"/>
-      <c r="H13" s="27" t="n"/>
-      <c r="I13" s="27" t="n"/>
-      <c r="J13" s="27" t="n"/>
-      <c r="K13" s="27" t="n"/>
-      <c r="L13" s="27" t="n"/>
-      <c r="M13" s="27" t="n"/>
-      <c r="N13" s="27" t="n"/>
-      <c r="O13" s="27" t="n"/>
-      <c r="P13" s="27" t="n"/>
-      <c r="Q13" s="27" t="n"/>
-      <c r="R13" s="27" t="n"/>
+      <c r="A13" s="28" t="n"/>
+      <c r="B13" s="28" t="n"/>
+      <c r="C13" s="28" t="n"/>
+      <c r="D13" s="28" t="n"/>
+      <c r="E13" s="28" t="n"/>
+      <c r="F13" s="28" t="n"/>
+      <c r="G13" s="28" t="n"/>
+      <c r="H13" s="28" t="n"/>
+      <c r="I13" s="28" t="n"/>
+      <c r="J13" s="28" t="n"/>
+      <c r="K13" s="28" t="n"/>
+      <c r="L13" s="28" t="n"/>
+      <c r="M13" s="28" t="n"/>
+      <c r="N13" s="28" t="n"/>
+      <c r="O13" s="28" t="n"/>
+      <c r="P13" s="28" t="n"/>
+      <c r="Q13" s="28" t="n"/>
+      <c r="R13" s="28" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="28" t="n"/>
-      <c r="B14" s="28" t="n"/>
-      <c r="C14" s="28" t="n"/>
-      <c r="D14" s="28" t="n"/>
-      <c r="E14" s="28" t="n"/>
-      <c r="F14" s="28" t="n"/>
-      <c r="G14" s="28" t="n"/>
-      <c r="H14" s="28" t="n"/>
-      <c r="I14" s="28" t="n"/>
-      <c r="J14" s="28" t="n"/>
-      <c r="K14" s="28" t="n"/>
-      <c r="L14" s="28" t="n"/>
-      <c r="M14" s="28" t="n"/>
-      <c r="N14" s="28" t="n"/>
-      <c r="O14" s="28" t="n"/>
-      <c r="P14" s="28" t="n"/>
-      <c r="Q14" s="28" t="n"/>
-      <c r="R14" s="28" t="n"/>
+      <c r="A14" s="29" t="n"/>
+      <c r="B14" s="29" t="n"/>
+      <c r="C14" s="29" t="n"/>
+      <c r="D14" s="29" t="n"/>
+      <c r="E14" s="29" t="n"/>
+      <c r="F14" s="29" t="n"/>
+      <c r="G14" s="29" t="n"/>
+      <c r="H14" s="29" t="n"/>
+      <c r="I14" s="29" t="n"/>
+      <c r="J14" s="29" t="n"/>
+      <c r="K14" s="29" t="n"/>
+      <c r="L14" s="29" t="n"/>
+      <c r="M14" s="29" t="n"/>
+      <c r="N14" s="29" t="n"/>
+      <c r="O14" s="29" t="n"/>
+      <c r="P14" s="29" t="n"/>
+      <c r="Q14" s="29" t="n"/>
+      <c r="R14" s="29" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="27" t="n"/>
-      <c r="B15" s="27" t="n"/>
-      <c r="C15" s="27" t="n"/>
-      <c r="D15" s="27" t="n"/>
-      <c r="E15" s="27" t="n"/>
-      <c r="F15" s="27" t="n"/>
-      <c r="G15" s="27" t="n"/>
-      <c r="H15" s="27" t="n"/>
-      <c r="I15" s="27" t="n"/>
-      <c r="J15" s="27" t="n"/>
-      <c r="K15" s="27" t="n"/>
-      <c r="L15" s="27" t="n"/>
-      <c r="M15" s="27" t="n"/>
-      <c r="N15" s="27" t="n"/>
-      <c r="O15" s="27" t="n"/>
-      <c r="P15" s="27" t="n"/>
-      <c r="Q15" s="27" t="n"/>
-      <c r="R15" s="27" t="n"/>
+      <c r="A15" s="28" t="n"/>
+      <c r="B15" s="28" t="n"/>
+      <c r="C15" s="28" t="n"/>
+      <c r="D15" s="28" t="n"/>
+      <c r="E15" s="28" t="n"/>
+      <c r="F15" s="28" t="n"/>
+      <c r="G15" s="28" t="n"/>
+      <c r="H15" s="28" t="n"/>
+      <c r="I15" s="28" t="n"/>
+      <c r="J15" s="28" t="n"/>
+      <c r="K15" s="28" t="n"/>
+      <c r="L15" s="28" t="n"/>
+      <c r="M15" s="28" t="n"/>
+      <c r="N15" s="28" t="n"/>
+      <c r="O15" s="28" t="n"/>
+      <c r="P15" s="28" t="n"/>
+      <c r="Q15" s="28" t="n"/>
+      <c r="R15" s="28" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="28" t="n"/>
-      <c r="B16" s="28" t="n"/>
-      <c r="C16" s="28" t="n"/>
-      <c r="D16" s="28" t="n"/>
-      <c r="E16" s="28" t="n"/>
-      <c r="F16" s="28" t="n"/>
-      <c r="G16" s="28" t="n"/>
-      <c r="H16" s="28" t="n"/>
-      <c r="I16" s="28" t="n"/>
-      <c r="J16" s="28" t="n"/>
-      <c r="K16" s="28" t="n"/>
-      <c r="L16" s="28" t="n"/>
-      <c r="M16" s="28" t="n"/>
-      <c r="N16" s="28" t="n"/>
-      <c r="O16" s="28" t="n"/>
-      <c r="P16" s="28" t="n"/>
-      <c r="Q16" s="28" t="n"/>
-      <c r="R16" s="28" t="n"/>
+      <c r="A16" s="29" t="n"/>
+      <c r="B16" s="29" t="n"/>
+      <c r="C16" s="29" t="n"/>
+      <c r="D16" s="29" t="n"/>
+      <c r="E16" s="29" t="n"/>
+      <c r="F16" s="29" t="n"/>
+      <c r="G16" s="29" t="n"/>
+      <c r="H16" s="29" t="n"/>
+      <c r="I16" s="29" t="n"/>
+      <c r="J16" s="29" t="n"/>
+      <c r="K16" s="29" t="n"/>
+      <c r="L16" s="29" t="n"/>
+      <c r="M16" s="29" t="n"/>
+      <c r="N16" s="29" t="n"/>
+      <c r="O16" s="29" t="n"/>
+      <c r="P16" s="29" t="n"/>
+      <c r="Q16" s="29" t="n"/>
+      <c r="R16" s="29" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="27" t="n"/>
-      <c r="B17" s="27" t="n"/>
-      <c r="C17" s="27" t="n"/>
-      <c r="D17" s="27" t="n"/>
-      <c r="E17" s="27" t="n"/>
-      <c r="F17" s="27" t="n"/>
-      <c r="G17" s="27" t="n"/>
-      <c r="H17" s="27" t="n"/>
-      <c r="I17" s="27" t="n"/>
-      <c r="J17" s="27" t="n"/>
-      <c r="K17" s="27" t="n"/>
-      <c r="L17" s="27" t="n"/>
-      <c r="M17" s="27" t="n"/>
-      <c r="N17" s="27" t="n"/>
-      <c r="O17" s="27" t="n"/>
-      <c r="P17" s="27" t="n"/>
-      <c r="Q17" s="27" t="n"/>
-      <c r="R17" s="27" t="n"/>
+      <c r="A17" s="28" t="n"/>
+      <c r="B17" s="28" t="n"/>
+      <c r="C17" s="28" t="n"/>
+      <c r="D17" s="28" t="n"/>
+      <c r="E17" s="28" t="n"/>
+      <c r="F17" s="28" t="n"/>
+      <c r="G17" s="28" t="n"/>
+      <c r="H17" s="28" t="n"/>
+      <c r="I17" s="28" t="n"/>
+      <c r="J17" s="28" t="n"/>
+      <c r="K17" s="28" t="n"/>
+      <c r="L17" s="28" t="n"/>
+      <c r="M17" s="28" t="n"/>
+      <c r="N17" s="28" t="n"/>
+      <c r="O17" s="28" t="n"/>
+      <c r="P17" s="28" t="n"/>
+      <c r="Q17" s="28" t="n"/>
+      <c r="R17" s="28" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="28" t="n"/>
-      <c r="B18" s="28" t="n"/>
-      <c r="C18" s="28" t="n"/>
-      <c r="D18" s="28" t="n"/>
-      <c r="E18" s="28" t="n"/>
-      <c r="F18" s="28" t="n"/>
-      <c r="G18" s="28" t="n"/>
-      <c r="H18" s="28" t="n"/>
-      <c r="I18" s="28" t="n"/>
-      <c r="J18" s="28" t="n"/>
-      <c r="K18" s="28" t="n"/>
-      <c r="L18" s="28" t="n"/>
-      <c r="M18" s="28" t="n"/>
-      <c r="N18" s="28" t="n"/>
-      <c r="O18" s="28" t="n"/>
-      <c r="P18" s="28" t="n"/>
-      <c r="Q18" s="28" t="n"/>
-      <c r="R18" s="28" t="n"/>
+      <c r="A18" s="29" t="n"/>
+      <c r="B18" s="29" t="n"/>
+      <c r="C18" s="29" t="n"/>
+      <c r="D18" s="29" t="n"/>
+      <c r="E18" s="29" t="n"/>
+      <c r="F18" s="29" t="n"/>
+      <c r="G18" s="29" t="n"/>
+      <c r="H18" s="29" t="n"/>
+      <c r="I18" s="29" t="n"/>
+      <c r="J18" s="29" t="n"/>
+      <c r="K18" s="29" t="n"/>
+      <c r="L18" s="29" t="n"/>
+      <c r="M18" s="29" t="n"/>
+      <c r="N18" s="29" t="n"/>
+      <c r="O18" s="29" t="n"/>
+      <c r="P18" s="29" t="n"/>
+      <c r="Q18" s="29" t="n"/>
+      <c r="R18" s="29" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="27" t="n"/>
-      <c r="B19" s="27" t="n"/>
-      <c r="C19" s="27" t="n"/>
-      <c r="D19" s="27" t="n"/>
-      <c r="E19" s="27" t="n"/>
-      <c r="F19" s="27" t="n"/>
-      <c r="G19" s="27" t="n"/>
-      <c r="H19" s="27" t="n"/>
-      <c r="I19" s="27" t="n"/>
-      <c r="J19" s="27" t="n"/>
-      <c r="K19" s="27" t="n"/>
-      <c r="L19" s="27" t="n"/>
-      <c r="M19" s="27" t="n"/>
-      <c r="N19" s="27" t="n"/>
-      <c r="O19" s="27" t="n"/>
-      <c r="P19" s="27" t="n"/>
-      <c r="Q19" s="27" t="n"/>
-      <c r="R19" s="27" t="n"/>
+      <c r="A19" s="28" t="n"/>
+      <c r="B19" s="28" t="n"/>
+      <c r="C19" s="28" t="n"/>
+      <c r="D19" s="28" t="n"/>
+      <c r="E19" s="28" t="n"/>
+      <c r="F19" s="28" t="n"/>
+      <c r="G19" s="28" t="n"/>
+      <c r="H19" s="28" t="n"/>
+      <c r="I19" s="28" t="n"/>
+      <c r="J19" s="28" t="n"/>
+      <c r="K19" s="28" t="n"/>
+      <c r="L19" s="28" t="n"/>
+      <c r="M19" s="28" t="n"/>
+      <c r="N19" s="28" t="n"/>
+      <c r="O19" s="28" t="n"/>
+      <c r="P19" s="28" t="n"/>
+      <c r="Q19" s="28" t="n"/>
+      <c r="R19" s="28" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="28" t="n"/>
-      <c r="B20" s="28" t="n"/>
-      <c r="C20" s="28" t="n"/>
-      <c r="D20" s="28" t="n"/>
-      <c r="E20" s="28" t="n"/>
-      <c r="F20" s="28" t="n"/>
-      <c r="G20" s="28" t="n"/>
-      <c r="H20" s="28" t="n"/>
-      <c r="I20" s="28" t="n"/>
-      <c r="J20" s="28" t="n"/>
-      <c r="K20" s="28" t="n"/>
-      <c r="L20" s="28" t="n"/>
-      <c r="M20" s="28" t="n"/>
-      <c r="N20" s="28" t="n"/>
-      <c r="O20" s="28" t="n"/>
-      <c r="P20" s="28" t="n"/>
-      <c r="Q20" s="28" t="n"/>
-      <c r="R20" s="28" t="n"/>
+      <c r="A20" s="29" t="n"/>
+      <c r="B20" s="29" t="n"/>
+      <c r="C20" s="29" t="n"/>
+      <c r="D20" s="29" t="n"/>
+      <c r="E20" s="29" t="n"/>
+      <c r="F20" s="29" t="n"/>
+      <c r="G20" s="29" t="n"/>
+      <c r="H20" s="29" t="n"/>
+      <c r="I20" s="29" t="n"/>
+      <c r="J20" s="29" t="n"/>
+      <c r="K20" s="29" t="n"/>
+      <c r="L20" s="29" t="n"/>
+      <c r="M20" s="29" t="n"/>
+      <c r="N20" s="29" t="n"/>
+      <c r="O20" s="29" t="n"/>
+      <c r="P20" s="29" t="n"/>
+      <c r="Q20" s="29" t="n"/>
+      <c r="R20" s="29" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="27" t="n"/>
-      <c r="B21" s="27" t="n"/>
-      <c r="C21" s="27" t="n"/>
-      <c r="D21" s="27" t="n"/>
-      <c r="E21" s="27" t="n"/>
-      <c r="F21" s="27" t="n"/>
-      <c r="G21" s="27" t="n"/>
-      <c r="H21" s="27" t="n"/>
-      <c r="I21" s="27" t="n"/>
-      <c r="J21" s="27" t="n"/>
-      <c r="K21" s="27" t="n"/>
-      <c r="L21" s="27" t="n"/>
-      <c r="M21" s="27" t="n"/>
-      <c r="N21" s="27" t="n"/>
-      <c r="O21" s="27" t="n"/>
-      <c r="P21" s="27" t="n"/>
-      <c r="Q21" s="27" t="n"/>
-      <c r="R21" s="27" t="n"/>
+      <c r="A21" s="28" t="n"/>
+      <c r="B21" s="28" t="n"/>
+      <c r="C21" s="28" t="n"/>
+      <c r="D21" s="28" t="n"/>
+      <c r="E21" s="28" t="n"/>
+      <c r="F21" s="28" t="n"/>
+      <c r="G21" s="28" t="n"/>
+      <c r="H21" s="28" t="n"/>
+      <c r="I21" s="28" t="n"/>
+      <c r="J21" s="28" t="n"/>
+      <c r="K21" s="28" t="n"/>
+      <c r="L21" s="28" t="n"/>
+      <c r="M21" s="28" t="n"/>
+      <c r="N21" s="28" t="n"/>
+      <c r="O21" s="28" t="n"/>
+      <c r="P21" s="28" t="n"/>
+      <c r="Q21" s="28" t="n"/>
+      <c r="R21" s="28" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="28" t="n"/>
-      <c r="B22" s="28" t="n"/>
-      <c r="C22" s="28" t="n"/>
-      <c r="D22" s="28" t="n"/>
-      <c r="E22" s="28" t="n"/>
-      <c r="F22" s="28" t="n"/>
-      <c r="G22" s="28" t="n"/>
-      <c r="H22" s="28" t="n"/>
-      <c r="I22" s="28" t="n"/>
-      <c r="J22" s="28" t="n"/>
-      <c r="K22" s="28" t="n"/>
-      <c r="L22" s="28" t="n"/>
-      <c r="M22" s="28" t="n"/>
-      <c r="N22" s="28" t="n"/>
-      <c r="O22" s="28" t="n"/>
-      <c r="P22" s="28" t="n"/>
-      <c r="Q22" s="28" t="n"/>
-      <c r="R22" s="28" t="n"/>
+      <c r="A22" s="29" t="n"/>
+      <c r="B22" s="29" t="n"/>
+      <c r="C22" s="29" t="n"/>
+      <c r="D22" s="29" t="n"/>
+      <c r="E22" s="29" t="n"/>
+      <c r="F22" s="29" t="n"/>
+      <c r="G22" s="29" t="n"/>
+      <c r="H22" s="29" t="n"/>
+      <c r="I22" s="29" t="n"/>
+      <c r="J22" s="29" t="n"/>
+      <c r="K22" s="29" t="n"/>
+      <c r="L22" s="29" t="n"/>
+      <c r="M22" s="29" t="n"/>
+      <c r="N22" s="29" t="n"/>
+      <c r="O22" s="29" t="n"/>
+      <c r="P22" s="29" t="n"/>
+      <c r="Q22" s="29" t="n"/>
+      <c r="R22" s="29" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="27" t="n"/>
-      <c r="B23" s="27" t="n"/>
-      <c r="C23" s="27" t="n"/>
-      <c r="D23" s="27" t="n"/>
-      <c r="E23" s="27" t="n"/>
-      <c r="F23" s="27" t="n"/>
-      <c r="G23" s="27" t="n"/>
-      <c r="H23" s="27" t="n"/>
-      <c r="I23" s="27" t="n"/>
-      <c r="J23" s="27" t="n"/>
-      <c r="K23" s="27" t="n"/>
-      <c r="L23" s="27" t="n"/>
-      <c r="M23" s="27" t="n"/>
-      <c r="N23" s="27" t="n"/>
-      <c r="O23" s="27" t="n"/>
-      <c r="P23" s="27" t="n"/>
-      <c r="Q23" s="27" t="n"/>
-      <c r="R23" s="27" t="n"/>
+      <c r="A23" s="28" t="n"/>
+      <c r="B23" s="28" t="n"/>
+      <c r="C23" s="28" t="n"/>
+      <c r="D23" s="28" t="n"/>
+      <c r="E23" s="28" t="n"/>
+      <c r="F23" s="28" t="n"/>
+      <c r="G23" s="28" t="n"/>
+      <c r="H23" s="28" t="n"/>
+      <c r="I23" s="28" t="n"/>
+      <c r="J23" s="28" t="n"/>
+      <c r="K23" s="28" t="n"/>
+      <c r="L23" s="28" t="n"/>
+      <c r="M23" s="28" t="n"/>
+      <c r="N23" s="28" t="n"/>
+      <c r="O23" s="28" t="n"/>
+      <c r="P23" s="28" t="n"/>
+      <c r="Q23" s="28" t="n"/>
+      <c r="R23" s="28" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="28" t="n"/>
-      <c r="B24" s="28" t="n"/>
-      <c r="C24" s="28" t="n"/>
-      <c r="D24" s="28" t="n"/>
-      <c r="E24" s="28" t="n"/>
-      <c r="F24" s="28" t="n"/>
-      <c r="G24" s="28" t="n"/>
-      <c r="H24" s="28" t="n"/>
-      <c r="I24" s="28" t="n"/>
-      <c r="J24" s="28" t="n"/>
-      <c r="K24" s="28" t="n"/>
-      <c r="L24" s="28" t="n"/>
-      <c r="M24" s="28" t="n"/>
-      <c r="N24" s="28" t="n"/>
-      <c r="O24" s="28" t="n"/>
-      <c r="P24" s="28" t="n"/>
-      <c r="Q24" s="28" t="n"/>
-      <c r="R24" s="28" t="n"/>
+      <c r="A24" s="29" t="n"/>
+      <c r="B24" s="29" t="n"/>
+      <c r="C24" s="29" t="n"/>
+      <c r="D24" s="29" t="n"/>
+      <c r="E24" s="29" t="n"/>
+      <c r="F24" s="29" t="n"/>
+      <c r="G24" s="29" t="n"/>
+      <c r="H24" s="29" t="n"/>
+      <c r="I24" s="29" t="n"/>
+      <c r="J24" s="29" t="n"/>
+      <c r="K24" s="29" t="n"/>
+      <c r="L24" s="29" t="n"/>
+      <c r="M24" s="29" t="n"/>
+      <c r="N24" s="29" t="n"/>
+      <c r="O24" s="29" t="n"/>
+      <c r="P24" s="29" t="n"/>
+      <c r="Q24" s="29" t="n"/>
+      <c r="R24" s="29" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="27" t="n"/>
-      <c r="B25" s="27" t="n"/>
-      <c r="C25" s="27" t="n"/>
-      <c r="D25" s="27" t="n"/>
-      <c r="E25" s="27" t="n"/>
-      <c r="F25" s="27" t="n"/>
-      <c r="G25" s="27" t="n"/>
-      <c r="H25" s="27" t="n"/>
-      <c r="I25" s="27" t="n"/>
-      <c r="J25" s="27" t="n"/>
-      <c r="K25" s="27" t="n"/>
-      <c r="L25" s="27" t="n"/>
-      <c r="M25" s="27" t="n"/>
-      <c r="N25" s="27" t="n"/>
-      <c r="O25" s="27" t="n"/>
-      <c r="P25" s="27" t="n"/>
-      <c r="Q25" s="27" t="n"/>
-      <c r="R25" s="27" t="n"/>
+      <c r="A25" s="28" t="n"/>
+      <c r="B25" s="28" t="n"/>
+      <c r="C25" s="28" t="n"/>
+      <c r="D25" s="28" t="n"/>
+      <c r="E25" s="28" t="n"/>
+      <c r="F25" s="28" t="n"/>
+      <c r="G25" s="28" t="n"/>
+      <c r="H25" s="28" t="n"/>
+      <c r="I25" s="28" t="n"/>
+      <c r="J25" s="28" t="n"/>
+      <c r="K25" s="28" t="n"/>
+      <c r="L25" s="28" t="n"/>
+      <c r="M25" s="28" t="n"/>
+      <c r="N25" s="28" t="n"/>
+      <c r="O25" s="28" t="n"/>
+      <c r="P25" s="28" t="n"/>
+      <c r="Q25" s="28" t="n"/>
+      <c r="R25" s="28" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="28" t="n"/>
-      <c r="B26" s="28" t="n"/>
-      <c r="C26" s="28" t="n"/>
-      <c r="D26" s="28" t="n"/>
-      <c r="E26" s="28" t="n"/>
-      <c r="F26" s="28" t="n"/>
-      <c r="G26" s="28" t="n"/>
-      <c r="H26" s="28" t="n"/>
-      <c r="I26" s="28" t="n"/>
-      <c r="J26" s="28" t="n"/>
-      <c r="K26" s="28" t="n"/>
-      <c r="L26" s="28" t="n"/>
-      <c r="M26" s="28" t="n"/>
-      <c r="N26" s="28" t="n"/>
-      <c r="O26" s="28" t="n"/>
-      <c r="P26" s="28" t="n"/>
-      <c r="Q26" s="28" t="n"/>
-      <c r="R26" s="28" t="n"/>
+      <c r="A26" s="29" t="n"/>
+      <c r="B26" s="29" t="n"/>
+      <c r="C26" s="29" t="n"/>
+      <c r="D26" s="29" t="n"/>
+      <c r="E26" s="29" t="n"/>
+      <c r="F26" s="29" t="n"/>
+      <c r="G26" s="29" t="n"/>
+      <c r="H26" s="29" t="n"/>
+      <c r="I26" s="29" t="n"/>
+      <c r="J26" s="29" t="n"/>
+      <c r="K26" s="29" t="n"/>
+      <c r="L26" s="29" t="n"/>
+      <c r="M26" s="29" t="n"/>
+      <c r="N26" s="29" t="n"/>
+      <c r="O26" s="29" t="n"/>
+      <c r="P26" s="29" t="n"/>
+      <c r="Q26" s="29" t="n"/>
+      <c r="R26" s="29" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="27" t="n"/>
-      <c r="B27" s="27" t="n"/>
-      <c r="C27" s="27" t="n"/>
-      <c r="D27" s="27" t="n"/>
-      <c r="E27" s="27" t="n"/>
-      <c r="F27" s="27" t="n"/>
-      <c r="G27" s="27" t="n"/>
-      <c r="H27" s="27" t="n"/>
-      <c r="I27" s="27" t="n"/>
-      <c r="J27" s="27" t="n"/>
-      <c r="K27" s="27" t="n"/>
-      <c r="L27" s="27" t="n"/>
-      <c r="M27" s="27" t="n"/>
-      <c r="N27" s="27" t="n"/>
-      <c r="O27" s="27" t="n"/>
-      <c r="P27" s="27" t="n"/>
-      <c r="Q27" s="27" t="n"/>
-      <c r="R27" s="27" t="n"/>
+      <c r="A27" s="28" t="n"/>
+      <c r="B27" s="28" t="n"/>
+      <c r="C27" s="28" t="n"/>
+      <c r="D27" s="28" t="n"/>
+      <c r="E27" s="28" t="n"/>
+      <c r="F27" s="28" t="n"/>
+      <c r="G27" s="28" t="n"/>
+      <c r="H27" s="28" t="n"/>
+      <c r="I27" s="28" t="n"/>
+      <c r="J27" s="28" t="n"/>
+      <c r="K27" s="28" t="n"/>
+      <c r="L27" s="28" t="n"/>
+      <c r="M27" s="28" t="n"/>
+      <c r="N27" s="28" t="n"/>
+      <c r="O27" s="28" t="n"/>
+      <c r="P27" s="28" t="n"/>
+      <c r="Q27" s="28" t="n"/>
+      <c r="R27" s="28" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="28" t="n"/>
-      <c r="B28" s="28" t="n"/>
-      <c r="C28" s="28" t="n"/>
-      <c r="D28" s="28" t="n"/>
-      <c r="E28" s="28" t="n"/>
-      <c r="F28" s="28" t="n"/>
-      <c r="G28" s="28" t="n"/>
-      <c r="H28" s="28" t="n"/>
-      <c r="I28" s="28" t="n"/>
-      <c r="J28" s="28" t="n"/>
-      <c r="K28" s="28" t="n"/>
-      <c r="L28" s="28" t="n"/>
-      <c r="M28" s="28" t="n"/>
-      <c r="N28" s="28" t="n"/>
-      <c r="O28" s="28" t="n"/>
-      <c r="P28" s="28" t="n"/>
-      <c r="Q28" s="28" t="n"/>
-      <c r="R28" s="28" t="n"/>
+      <c r="A28" s="29" t="n"/>
+      <c r="B28" s="29" t="n"/>
+      <c r="C28" s="29" t="n"/>
+      <c r="D28" s="29" t="n"/>
+      <c r="E28" s="29" t="n"/>
+      <c r="F28" s="29" t="n"/>
+      <c r="G28" s="29" t="n"/>
+      <c r="H28" s="29" t="n"/>
+      <c r="I28" s="29" t="n"/>
+      <c r="J28" s="29" t="n"/>
+      <c r="K28" s="29" t="n"/>
+      <c r="L28" s="29" t="n"/>
+      <c r="M28" s="29" t="n"/>
+      <c r="N28" s="29" t="n"/>
+      <c r="O28" s="29" t="n"/>
+      <c r="P28" s="29" t="n"/>
+      <c r="Q28" s="29" t="n"/>
+      <c r="R28" s="29" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="27" t="n"/>
-      <c r="B29" s="27" t="n"/>
-      <c r="C29" s="27" t="n"/>
-      <c r="D29" s="27" t="n"/>
-      <c r="E29" s="27" t="n"/>
-      <c r="F29" s="27" t="n"/>
-      <c r="G29" s="27" t="n"/>
-      <c r="H29" s="27" t="n"/>
-      <c r="I29" s="27" t="n"/>
-      <c r="J29" s="27" t="n"/>
-      <c r="K29" s="27" t="n"/>
-      <c r="L29" s="27" t="n"/>
-      <c r="M29" s="27" t="n"/>
-      <c r="N29" s="27" t="n"/>
-      <c r="O29" s="27" t="n"/>
-      <c r="P29" s="27" t="n"/>
-      <c r="Q29" s="27" t="n"/>
-      <c r="R29" s="27" t="n"/>
+      <c r="A29" s="28" t="n"/>
+      <c r="B29" s="28" t="n"/>
+      <c r="C29" s="28" t="n"/>
+      <c r="D29" s="28" t="n"/>
+      <c r="E29" s="28" t="n"/>
+      <c r="F29" s="28" t="n"/>
+      <c r="G29" s="28" t="n"/>
+      <c r="H29" s="28" t="n"/>
+      <c r="I29" s="28" t="n"/>
+      <c r="J29" s="28" t="n"/>
+      <c r="K29" s="28" t="n"/>
+      <c r="L29" s="28" t="n"/>
+      <c r="M29" s="28" t="n"/>
+      <c r="N29" s="28" t="n"/>
+      <c r="O29" s="28" t="n"/>
+      <c r="P29" s="28" t="n"/>
+      <c r="Q29" s="28" t="n"/>
+      <c r="R29" s="28" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="28" t="n"/>
-      <c r="B30" s="28" t="n"/>
-      <c r="C30" s="28" t="n"/>
-      <c r="D30" s="28" t="n"/>
-      <c r="E30" s="28" t="n"/>
-      <c r="F30" s="28" t="n"/>
-      <c r="G30" s="28" t="n"/>
-      <c r="H30" s="28" t="n"/>
-      <c r="I30" s="28" t="n"/>
-      <c r="J30" s="28" t="n"/>
-      <c r="K30" s="28" t="n"/>
-      <c r="L30" s="28" t="n"/>
-      <c r="M30" s="28" t="n"/>
-      <c r="N30" s="28" t="n"/>
-      <c r="O30" s="28" t="n"/>
-      <c r="P30" s="28" t="n"/>
-      <c r="Q30" s="28" t="n"/>
-      <c r="R30" s="28" t="n"/>
+      <c r="A30" s="29" t="n"/>
+      <c r="B30" s="29" t="n"/>
+      <c r="C30" s="29" t="n"/>
+      <c r="D30" s="29" t="n"/>
+      <c r="E30" s="29" t="n"/>
+      <c r="F30" s="29" t="n"/>
+      <c r="G30" s="29" t="n"/>
+      <c r="H30" s="29" t="n"/>
+      <c r="I30" s="29" t="n"/>
+      <c r="J30" s="29" t="n"/>
+      <c r="K30" s="29" t="n"/>
+      <c r="L30" s="29" t="n"/>
+      <c r="M30" s="29" t="n"/>
+      <c r="N30" s="29" t="n"/>
+      <c r="O30" s="29" t="n"/>
+      <c r="P30" s="29" t="n"/>
+      <c r="Q30" s="29" t="n"/>
+      <c r="R30" s="29" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="27" t="n"/>
-      <c r="B31" s="27" t="n"/>
-      <c r="C31" s="27" t="n"/>
-      <c r="D31" s="27" t="n"/>
-      <c r="E31" s="27" t="n"/>
-      <c r="F31" s="27" t="n"/>
-      <c r="G31" s="27" t="n"/>
-      <c r="H31" s="27" t="n"/>
-      <c r="I31" s="27" t="n"/>
-      <c r="J31" s="27" t="n"/>
-      <c r="K31" s="27" t="n"/>
-      <c r="L31" s="27" t="n"/>
-      <c r="M31" s="27" t="n"/>
-      <c r="N31" s="27" t="n"/>
-      <c r="O31" s="27" t="n"/>
-      <c r="P31" s="27" t="n"/>
-      <c r="Q31" s="27" t="n"/>
-      <c r="R31" s="27" t="n"/>
+      <c r="A31" s="28" t="n"/>
+      <c r="B31" s="28" t="n"/>
+      <c r="C31" s="28" t="n"/>
+      <c r="D31" s="28" t="n"/>
+      <c r="E31" s="28" t="n"/>
+      <c r="F31" s="28" t="n"/>
+      <c r="G31" s="28" t="n"/>
+      <c r="H31" s="28" t="n"/>
+      <c r="I31" s="28" t="n"/>
+      <c r="J31" s="28" t="n"/>
+      <c r="K31" s="28" t="n"/>
+      <c r="L31" s="28" t="n"/>
+      <c r="M31" s="28" t="n"/>
+      <c r="N31" s="28" t="n"/>
+      <c r="O31" s="28" t="n"/>
+      <c r="P31" s="28" t="n"/>
+      <c r="Q31" s="28" t="n"/>
+      <c r="R31" s="28" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="28" t="n"/>
-      <c r="B32" s="28" t="n"/>
-      <c r="C32" s="28" t="n"/>
-      <c r="D32" s="28" t="n"/>
-      <c r="E32" s="28" t="n"/>
-      <c r="F32" s="28" t="n"/>
-      <c r="G32" s="28" t="n"/>
-      <c r="H32" s="28" t="n"/>
-      <c r="I32" s="28" t="n"/>
-      <c r="J32" s="28" t="n"/>
-      <c r="K32" s="28" t="n"/>
-      <c r="L32" s="28" t="n"/>
-      <c r="M32" s="28" t="n"/>
-      <c r="N32" s="28" t="n"/>
-      <c r="O32" s="28" t="n"/>
-      <c r="P32" s="28" t="n"/>
-      <c r="Q32" s="28" t="n"/>
-      <c r="R32" s="28" t="n"/>
+      <c r="A32" s="29" t="n"/>
+      <c r="B32" s="29" t="n"/>
+      <c r="C32" s="29" t="n"/>
+      <c r="D32" s="29" t="n"/>
+      <c r="E32" s="29" t="n"/>
+      <c r="F32" s="29" t="n"/>
+      <c r="G32" s="29" t="n"/>
+      <c r="H32" s="29" t="n"/>
+      <c r="I32" s="29" t="n"/>
+      <c r="J32" s="29" t="n"/>
+      <c r="K32" s="29" t="n"/>
+      <c r="L32" s="29" t="n"/>
+      <c r="M32" s="29" t="n"/>
+      <c r="N32" s="29" t="n"/>
+      <c r="O32" s="29" t="n"/>
+      <c r="P32" s="29" t="n"/>
+      <c r="Q32" s="29" t="n"/>
+      <c r="R32" s="29" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="27" t="n"/>
-      <c r="B33" s="27" t="n"/>
-      <c r="C33" s="27" t="n"/>
-      <c r="D33" s="27" t="n"/>
-      <c r="E33" s="27" t="n"/>
-      <c r="F33" s="27" t="n"/>
-      <c r="G33" s="27" t="n"/>
-      <c r="H33" s="27" t="n"/>
-      <c r="I33" s="27" t="n"/>
-      <c r="J33" s="27" t="n"/>
-      <c r="K33" s="27" t="n"/>
-      <c r="L33" s="27" t="n"/>
-      <c r="M33" s="27" t="n"/>
-      <c r="N33" s="27" t="n"/>
-      <c r="O33" s="27" t="n"/>
-      <c r="P33" s="27" t="n"/>
-      <c r="Q33" s="27" t="n"/>
-      <c r="R33" s="27" t="n"/>
+      <c r="A33" s="28" t="n"/>
+      <c r="B33" s="28" t="n"/>
+      <c r="C33" s="28" t="n"/>
+      <c r="D33" s="28" t="n"/>
+      <c r="E33" s="28" t="n"/>
+      <c r="F33" s="28" t="n"/>
+      <c r="G33" s="28" t="n"/>
+      <c r="H33" s="28" t="n"/>
+      <c r="I33" s="28" t="n"/>
+      <c r="J33" s="28" t="n"/>
+      <c r="K33" s="28" t="n"/>
+      <c r="L33" s="28" t="n"/>
+      <c r="M33" s="28" t="n"/>
+      <c r="N33" s="28" t="n"/>
+      <c r="O33" s="28" t="n"/>
+      <c r="P33" s="28" t="n"/>
+      <c r="Q33" s="28" t="n"/>
+      <c r="R33" s="28" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="28" t="n"/>
-      <c r="B34" s="28" t="n"/>
-      <c r="C34" s="28" t="n"/>
-      <c r="D34" s="28" t="n"/>
-      <c r="E34" s="28" t="n"/>
-      <c r="F34" s="28" t="n"/>
-      <c r="G34" s="28" t="n"/>
-      <c r="H34" s="28" t="n"/>
-      <c r="I34" s="28" t="n"/>
-      <c r="J34" s="28" t="n"/>
-      <c r="K34" s="28" t="n"/>
-      <c r="L34" s="28" t="n"/>
-      <c r="M34" s="28" t="n"/>
-      <c r="N34" s="28" t="n"/>
-      <c r="O34" s="28" t="n"/>
-      <c r="P34" s="28" t="n"/>
-      <c r="Q34" s="28" t="n"/>
-      <c r="R34" s="28" t="n"/>
+      <c r="A34" s="29" t="n"/>
+      <c r="B34" s="29" t="n"/>
+      <c r="C34" s="29" t="n"/>
+      <c r="D34" s="29" t="n"/>
+      <c r="E34" s="29" t="n"/>
+      <c r="F34" s="29" t="n"/>
+      <c r="G34" s="29" t="n"/>
+      <c r="H34" s="29" t="n"/>
+      <c r="I34" s="29" t="n"/>
+      <c r="J34" s="29" t="n"/>
+      <c r="K34" s="29" t="n"/>
+      <c r="L34" s="29" t="n"/>
+      <c r="M34" s="29" t="n"/>
+      <c r="N34" s="29" t="n"/>
+      <c r="O34" s="29" t="n"/>
+      <c r="P34" s="29" t="n"/>
+      <c r="Q34" s="29" t="n"/>
+      <c r="R34" s="29" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="27" t="n"/>
-      <c r="B35" s="27" t="n"/>
-      <c r="C35" s="27" t="n"/>
-      <c r="D35" s="27" t="n"/>
-      <c r="E35" s="27" t="n"/>
-      <c r="F35" s="27" t="n"/>
-      <c r="G35" s="27" t="n"/>
-      <c r="H35" s="27" t="n"/>
-      <c r="I35" s="27" t="n"/>
-      <c r="J35" s="27" t="n"/>
-      <c r="K35" s="27" t="n"/>
-      <c r="L35" s="27" t="n"/>
-      <c r="M35" s="27" t="n"/>
-      <c r="N35" s="27" t="n"/>
-      <c r="O35" s="27" t="n"/>
-      <c r="P35" s="27" t="n"/>
-      <c r="Q35" s="27" t="n"/>
-      <c r="R35" s="27" t="n"/>
+      <c r="A35" s="28" t="n"/>
+      <c r="B35" s="28" t="n"/>
+      <c r="C35" s="28" t="n"/>
+      <c r="D35" s="28" t="n"/>
+      <c r="E35" s="28" t="n"/>
+      <c r="F35" s="28" t="n"/>
+      <c r="G35" s="28" t="n"/>
+      <c r="H35" s="28" t="n"/>
+      <c r="I35" s="28" t="n"/>
+      <c r="J35" s="28" t="n"/>
+      <c r="K35" s="28" t="n"/>
+      <c r="L35" s="28" t="n"/>
+      <c r="M35" s="28" t="n"/>
+      <c r="N35" s="28" t="n"/>
+      <c r="O35" s="28" t="n"/>
+      <c r="P35" s="28" t="n"/>
+      <c r="Q35" s="28" t="n"/>
+      <c r="R35" s="28" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="28" t="n"/>
-      <c r="B36" s="28" t="n"/>
-      <c r="C36" s="28" t="n"/>
-      <c r="D36" s="28" t="n"/>
-      <c r="E36" s="28" t="n"/>
-      <c r="F36" s="28" t="n"/>
-      <c r="G36" s="28" t="n"/>
-      <c r="H36" s="28" t="n"/>
-      <c r="I36" s="28" t="n"/>
-      <c r="J36" s="28" t="n"/>
-      <c r="K36" s="28" t="n"/>
-      <c r="L36" s="28" t="n"/>
-      <c r="M36" s="28" t="n"/>
-      <c r="N36" s="28" t="n"/>
-      <c r="O36" s="28" t="n"/>
-      <c r="P36" s="28" t="n"/>
-      <c r="Q36" s="28" t="n"/>
-      <c r="R36" s="28" t="n"/>
+      <c r="A36" s="29" t="n"/>
+      <c r="B36" s="29" t="n"/>
+      <c r="C36" s="29" t="n"/>
+      <c r="D36" s="29" t="n"/>
+      <c r="E36" s="29" t="n"/>
+      <c r="F36" s="29" t="n"/>
+      <c r="G36" s="29" t="n"/>
+      <c r="H36" s="29" t="n"/>
+      <c r="I36" s="29" t="n"/>
+      <c r="J36" s="29" t="n"/>
+      <c r="K36" s="29" t="n"/>
+      <c r="L36" s="29" t="n"/>
+      <c r="M36" s="29" t="n"/>
+      <c r="N36" s="29" t="n"/>
+      <c r="O36" s="29" t="n"/>
+      <c r="P36" s="29" t="n"/>
+      <c r="Q36" s="29" t="n"/>
+      <c r="R36" s="29" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="27" t="n"/>
-      <c r="B37" s="27" t="n"/>
-      <c r="C37" s="27" t="n"/>
-      <c r="D37" s="27" t="n"/>
-      <c r="E37" s="27" t="n"/>
-      <c r="F37" s="27" t="n"/>
-      <c r="G37" s="27" t="n"/>
-      <c r="H37" s="27" t="n"/>
-      <c r="I37" s="27" t="n"/>
-      <c r="J37" s="27" t="n"/>
-      <c r="K37" s="27" t="n"/>
-      <c r="L37" s="27" t="n"/>
-      <c r="M37" s="27" t="n"/>
-      <c r="N37" s="27" t="n"/>
-      <c r="O37" s="27" t="n"/>
-      <c r="P37" s="27" t="n"/>
-      <c r="Q37" s="27" t="n"/>
-      <c r="R37" s="27" t="n"/>
+      <c r="A37" s="28" t="n"/>
+      <c r="B37" s="28" t="n"/>
+      <c r="C37" s="28" t="n"/>
+      <c r="D37" s="28" t="n"/>
+      <c r="E37" s="28" t="n"/>
+      <c r="F37" s="28" t="n"/>
+      <c r="G37" s="28" t="n"/>
+      <c r="H37" s="28" t="n"/>
+      <c r="I37" s="28" t="n"/>
+      <c r="J37" s="28" t="n"/>
+      <c r="K37" s="28" t="n"/>
+      <c r="L37" s="28" t="n"/>
+      <c r="M37" s="28" t="n"/>
+      <c r="N37" s="28" t="n"/>
+      <c r="O37" s="28" t="n"/>
+      <c r="P37" s="28" t="n"/>
+      <c r="Q37" s="28" t="n"/>
+      <c r="R37" s="28" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="28" t="n"/>
-      <c r="B38" s="28" t="n"/>
-      <c r="C38" s="28" t="n"/>
-      <c r="D38" s="28" t="n"/>
-      <c r="E38" s="28" t="n"/>
-      <c r="F38" s="28" t="n"/>
-      <c r="G38" s="28" t="n"/>
-      <c r="H38" s="28" t="n"/>
-      <c r="I38" s="28" t="n"/>
-      <c r="J38" s="28" t="n"/>
-      <c r="K38" s="28" t="n"/>
-      <c r="L38" s="28" t="n"/>
-      <c r="M38" s="28" t="n"/>
-      <c r="N38" s="28" t="n"/>
-      <c r="O38" s="28" t="n"/>
-      <c r="P38" s="28" t="n"/>
-      <c r="Q38" s="28" t="n"/>
-      <c r="R38" s="28" t="n"/>
+      <c r="A38" s="29" t="n"/>
+      <c r="B38" s="29" t="n"/>
+      <c r="C38" s="29" t="n"/>
+      <c r="D38" s="29" t="n"/>
+      <c r="E38" s="29" t="n"/>
+      <c r="F38" s="29" t="n"/>
+      <c r="G38" s="29" t="n"/>
+      <c r="H38" s="29" t="n"/>
+      <c r="I38" s="29" t="n"/>
+      <c r="J38" s="29" t="n"/>
+      <c r="K38" s="29" t="n"/>
+      <c r="L38" s="29" t="n"/>
+      <c r="M38" s="29" t="n"/>
+      <c r="N38" s="29" t="n"/>
+      <c r="O38" s="29" t="n"/>
+      <c r="P38" s="29" t="n"/>
+      <c r="Q38" s="29" t="n"/>
+      <c r="R38" s="29" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="27" t="n"/>
-      <c r="B39" s="27" t="n"/>
-      <c r="C39" s="27" t="n"/>
-      <c r="D39" s="27" t="n"/>
-      <c r="E39" s="27" t="n"/>
-      <c r="F39" s="27" t="n"/>
-      <c r="G39" s="27" t="n"/>
-      <c r="H39" s="27" t="n"/>
-      <c r="I39" s="27" t="n"/>
-      <c r="J39" s="27" t="n"/>
-      <c r="K39" s="27" t="n"/>
-      <c r="L39" s="27" t="n"/>
-      <c r="M39" s="27" t="n"/>
-      <c r="N39" s="27" t="n"/>
-      <c r="O39" s="27" t="n"/>
-      <c r="P39" s="27" t="n"/>
-      <c r="Q39" s="27" t="n"/>
-      <c r="R39" s="27" t="n"/>
+      <c r="A39" s="28" t="n"/>
+      <c r="B39" s="28" t="n"/>
+      <c r="C39" s="28" t="n"/>
+      <c r="D39" s="28" t="n"/>
+      <c r="E39" s="28" t="n"/>
+      <c r="F39" s="28" t="n"/>
+      <c r="G39" s="28" t="n"/>
+      <c r="H39" s="28" t="n"/>
+      <c r="I39" s="28" t="n"/>
+      <c r="J39" s="28" t="n"/>
+      <c r="K39" s="28" t="n"/>
+      <c r="L39" s="28" t="n"/>
+      <c r="M39" s="28" t="n"/>
+      <c r="N39" s="28" t="n"/>
+      <c r="O39" s="28" t="n"/>
+      <c r="P39" s="28" t="n"/>
+      <c r="Q39" s="28" t="n"/>
+      <c r="R39" s="28" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="28" t="n"/>
-      <c r="B40" s="28" t="n"/>
-      <c r="C40" s="28" t="n"/>
-      <c r="D40" s="28" t="n"/>
-      <c r="E40" s="28" t="n"/>
-      <c r="F40" s="28" t="n"/>
-      <c r="G40" s="28" t="n"/>
-      <c r="H40" s="28" t="n"/>
-      <c r="I40" s="28" t="n"/>
-      <c r="J40" s="28" t="n"/>
-      <c r="K40" s="28" t="n"/>
-      <c r="L40" s="28" t="n"/>
-      <c r="M40" s="28" t="n"/>
-      <c r="N40" s="28" t="n"/>
-      <c r="O40" s="28" t="n"/>
-      <c r="P40" s="28" t="n"/>
-      <c r="Q40" s="28" t="n"/>
-      <c r="R40" s="28" t="n"/>
+      <c r="A40" s="29" t="n"/>
+      <c r="B40" s="29" t="n"/>
+      <c r="C40" s="29" t="n"/>
+      <c r="D40" s="29" t="n"/>
+      <c r="E40" s="29" t="n"/>
+      <c r="F40" s="29" t="n"/>
+      <c r="G40" s="29" t="n"/>
+      <c r="H40" s="29" t="n"/>
+      <c r="I40" s="29" t="n"/>
+      <c r="J40" s="29" t="n"/>
+      <c r="K40" s="29" t="n"/>
+      <c r="L40" s="29" t="n"/>
+      <c r="M40" s="29" t="n"/>
+      <c r="N40" s="29" t="n"/>
+      <c r="O40" s="29" t="n"/>
+      <c r="P40" s="29" t="n"/>
+      <c r="Q40" s="29" t="n"/>
+      <c r="R40" s="29" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="27" t="n"/>
-      <c r="B41" s="27" t="n"/>
-      <c r="C41" s="27" t="n"/>
-      <c r="D41" s="27" t="n"/>
-      <c r="E41" s="27" t="n"/>
-      <c r="F41" s="27" t="n"/>
-      <c r="G41" s="27" t="n"/>
-      <c r="H41" s="27" t="n"/>
-      <c r="I41" s="27" t="n"/>
-      <c r="J41" s="27" t="n"/>
-      <c r="K41" s="27" t="n"/>
-      <c r="L41" s="27" t="n"/>
-      <c r="M41" s="27" t="n"/>
-      <c r="N41" s="27" t="n"/>
-      <c r="O41" s="27" t="n"/>
-      <c r="P41" s="27" t="n"/>
-      <c r="Q41" s="27" t="n"/>
-      <c r="R41" s="27" t="n"/>
+      <c r="A41" s="28" t="n"/>
+      <c r="B41" s="28" t="n"/>
+      <c r="C41" s="28" t="n"/>
+      <c r="D41" s="28" t="n"/>
+      <c r="E41" s="28" t="n"/>
+      <c r="F41" s="28" t="n"/>
+      <c r="G41" s="28" t="n"/>
+      <c r="H41" s="28" t="n"/>
+      <c r="I41" s="28" t="n"/>
+      <c r="J41" s="28" t="n"/>
+      <c r="K41" s="28" t="n"/>
+      <c r="L41" s="28" t="n"/>
+      <c r="M41" s="28" t="n"/>
+      <c r="N41" s="28" t="n"/>
+      <c r="O41" s="28" t="n"/>
+      <c r="P41" s="28" t="n"/>
+      <c r="Q41" s="28" t="n"/>
+      <c r="R41" s="28" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="28" t="n"/>
-      <c r="B42" s="28" t="n"/>
-      <c r="C42" s="28" t="n"/>
-      <c r="D42" s="28" t="n"/>
-      <c r="E42" s="28" t="n"/>
-      <c r="F42" s="28" t="n"/>
-      <c r="G42" s="28" t="n"/>
-      <c r="H42" s="28" t="n"/>
-      <c r="I42" s="28" t="n"/>
-      <c r="J42" s="28" t="n"/>
-      <c r="K42" s="28" t="n"/>
-      <c r="L42" s="28" t="n"/>
-      <c r="M42" s="28" t="n"/>
-      <c r="N42" s="28" t="n"/>
-      <c r="O42" s="28" t="n"/>
-      <c r="P42" s="28" t="n"/>
-      <c r="Q42" s="28" t="n"/>
-      <c r="R42" s="28" t="n"/>
+      <c r="A42" s="29" t="n"/>
+      <c r="B42" s="29" t="n"/>
+      <c r="C42" s="29" t="n"/>
+      <c r="D42" s="29" t="n"/>
+      <c r="E42" s="29" t="n"/>
+      <c r="F42" s="29" t="n"/>
+      <c r="G42" s="29" t="n"/>
+      <c r="H42" s="29" t="n"/>
+      <c r="I42" s="29" t="n"/>
+      <c r="J42" s="29" t="n"/>
+      <c r="K42" s="29" t="n"/>
+      <c r="L42" s="29" t="n"/>
+      <c r="M42" s="29" t="n"/>
+      <c r="N42" s="29" t="n"/>
+      <c r="O42" s="29" t="n"/>
+      <c r="P42" s="29" t="n"/>
+      <c r="Q42" s="29" t="n"/>
+      <c r="R42" s="29" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="27" t="n"/>
-      <c r="B43" s="27" t="n"/>
-      <c r="C43" s="27" t="n"/>
-      <c r="D43" s="27" t="n"/>
-      <c r="E43" s="27" t="n"/>
-      <c r="F43" s="27" t="n"/>
-      <c r="G43" s="27" t="n"/>
-      <c r="H43" s="27" t="n"/>
-      <c r="I43" s="27" t="n"/>
-      <c r="J43" s="27" t="n"/>
-      <c r="K43" s="27" t="n"/>
-      <c r="L43" s="27" t="n"/>
-      <c r="M43" s="27" t="n"/>
-      <c r="N43" s="27" t="n"/>
-      <c r="O43" s="27" t="n"/>
-      <c r="P43" s="27" t="n"/>
-      <c r="Q43" s="27" t="n"/>
-      <c r="R43" s="27" t="n"/>
+      <c r="A43" s="28" t="n"/>
+      <c r="B43" s="28" t="n"/>
+      <c r="C43" s="28" t="n"/>
+      <c r="D43" s="28" t="n"/>
+      <c r="E43" s="28" t="n"/>
+      <c r="F43" s="28" t="n"/>
+      <c r="G43" s="28" t="n"/>
+      <c r="H43" s="28" t="n"/>
+      <c r="I43" s="28" t="n"/>
+      <c r="J43" s="28" t="n"/>
+      <c r="K43" s="28" t="n"/>
+      <c r="L43" s="28" t="n"/>
+      <c r="M43" s="28" t="n"/>
+      <c r="N43" s="28" t="n"/>
+      <c r="O43" s="28" t="n"/>
+      <c r="P43" s="28" t="n"/>
+      <c r="Q43" s="28" t="n"/>
+      <c r="R43" s="28" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" s="28" t="n"/>
-      <c r="B44" s="28" t="n"/>
-      <c r="C44" s="28" t="n"/>
-      <c r="D44" s="28" t="n"/>
-      <c r="E44" s="28" t="n"/>
-      <c r="F44" s="28" t="n"/>
-      <c r="G44" s="28" t="n"/>
-      <c r="H44" s="28" t="n"/>
-      <c r="I44" s="28" t="n"/>
-      <c r="J44" s="28" t="n"/>
-      <c r="K44" s="28" t="n"/>
-      <c r="L44" s="28" t="n"/>
-      <c r="M44" s="28" t="n"/>
-      <c r="N44" s="28" t="n"/>
-      <c r="O44" s="28" t="n"/>
-      <c r="P44" s="28" t="n"/>
-      <c r="Q44" s="28" t="n"/>
-      <c r="R44" s="28" t="n"/>
+      <c r="A44" s="29" t="n"/>
+      <c r="B44" s="29" t="n"/>
+      <c r="C44" s="29" t="n"/>
+      <c r="D44" s="29" t="n"/>
+      <c r="E44" s="29" t="n"/>
+      <c r="F44" s="29" t="n"/>
+      <c r="G44" s="29" t="n"/>
+      <c r="H44" s="29" t="n"/>
+      <c r="I44" s="29" t="n"/>
+      <c r="J44" s="29" t="n"/>
+      <c r="K44" s="29" t="n"/>
+      <c r="L44" s="29" t="n"/>
+      <c r="M44" s="29" t="n"/>
+      <c r="N44" s="29" t="n"/>
+      <c r="O44" s="29" t="n"/>
+      <c r="P44" s="29" t="n"/>
+      <c r="Q44" s="29" t="n"/>
+      <c r="R44" s="29" t="n"/>
     </row>
     <row r="45">
-      <c r="A45" s="27" t="n"/>
-      <c r="B45" s="27" t="n"/>
-      <c r="C45" s="27" t="n"/>
-      <c r="D45" s="27" t="n"/>
-      <c r="E45" s="27" t="n"/>
-      <c r="F45" s="27" t="n"/>
-      <c r="G45" s="27" t="n"/>
-      <c r="H45" s="27" t="n"/>
-      <c r="I45" s="27" t="n"/>
-      <c r="J45" s="27" t="n"/>
-      <c r="K45" s="27" t="n"/>
-      <c r="L45" s="27" t="n"/>
-      <c r="M45" s="27" t="n"/>
-      <c r="N45" s="27" t="n"/>
-      <c r="O45" s="27" t="n"/>
-      <c r="P45" s="27" t="n"/>
-      <c r="Q45" s="27" t="n"/>
-      <c r="R45" s="27" t="n"/>
+      <c r="A45" s="28" t="n"/>
+      <c r="B45" s="28" t="n"/>
+      <c r="C45" s="28" t="n"/>
+      <c r="D45" s="28" t="n"/>
+      <c r="E45" s="28" t="n"/>
+      <c r="F45" s="28" t="n"/>
+      <c r="G45" s="28" t="n"/>
+      <c r="H45" s="28" t="n"/>
+      <c r="I45" s="28" t="n"/>
+      <c r="J45" s="28" t="n"/>
+      <c r="K45" s="28" t="n"/>
+      <c r="L45" s="28" t="n"/>
+      <c r="M45" s="28" t="n"/>
+      <c r="N45" s="28" t="n"/>
+      <c r="O45" s="28" t="n"/>
+      <c r="P45" s="28" t="n"/>
+      <c r="Q45" s="28" t="n"/>
+      <c r="R45" s="28" t="n"/>
     </row>
     <row r="46">
-      <c r="A46" s="28" t="n"/>
-      <c r="B46" s="28" t="n"/>
-      <c r="C46" s="28" t="n"/>
-      <c r="D46" s="28" t="n"/>
-      <c r="E46" s="28" t="n"/>
-      <c r="F46" s="28" t="n"/>
-      <c r="G46" s="28" t="n"/>
-      <c r="H46" s="28" t="n"/>
-      <c r="I46" s="28" t="n"/>
-      <c r="J46" s="28" t="n"/>
-      <c r="K46" s="28" t="n"/>
-      <c r="L46" s="28" t="n"/>
-      <c r="M46" s="28" t="n"/>
-      <c r="N46" s="28" t="n"/>
-      <c r="O46" s="28" t="n"/>
-      <c r="P46" s="28" t="n"/>
-      <c r="Q46" s="28" t="n"/>
-      <c r="R46" s="28" t="n"/>
+      <c r="A46" s="29" t="n"/>
+      <c r="B46" s="29" t="n"/>
+      <c r="C46" s="29" t="n"/>
+      <c r="D46" s="29" t="n"/>
+      <c r="E46" s="29" t="n"/>
+      <c r="F46" s="29" t="n"/>
+      <c r="G46" s="29" t="n"/>
+      <c r="H46" s="29" t="n"/>
+      <c r="I46" s="29" t="n"/>
+      <c r="J46" s="29" t="n"/>
+      <c r="K46" s="29" t="n"/>
+      <c r="L46" s="29" t="n"/>
+      <c r="M46" s="29" t="n"/>
+      <c r="N46" s="29" t="n"/>
+      <c r="O46" s="29" t="n"/>
+      <c r="P46" s="29" t="n"/>
+      <c r="Q46" s="29" t="n"/>
+      <c r="R46" s="29" t="n"/>
     </row>
     <row r="47">
-      <c r="A47" s="27" t="n"/>
-      <c r="B47" s="27" t="n"/>
-      <c r="C47" s="27" t="n"/>
-      <c r="D47" s="27" t="n"/>
-      <c r="E47" s="27" t="n"/>
-      <c r="F47" s="27" t="n"/>
-      <c r="G47" s="27" t="n"/>
-      <c r="H47" s="27" t="n"/>
-      <c r="I47" s="27" t="n"/>
-      <c r="J47" s="27" t="n"/>
-      <c r="K47" s="27" t="n"/>
-      <c r="L47" s="27" t="n"/>
-      <c r="M47" s="27" t="n"/>
-      <c r="N47" s="27" t="n"/>
-      <c r="O47" s="27" t="n"/>
-      <c r="P47" s="27" t="n"/>
-      <c r="Q47" s="27" t="n"/>
-      <c r="R47" s="27" t="n"/>
+      <c r="A47" s="28" t="n"/>
+      <c r="B47" s="28" t="n"/>
+      <c r="C47" s="28" t="n"/>
+      <c r="D47" s="28" t="n"/>
+      <c r="E47" s="28" t="n"/>
+      <c r="F47" s="28" t="n"/>
+      <c r="G47" s="28" t="n"/>
+      <c r="H47" s="28" t="n"/>
+      <c r="I47" s="28" t="n"/>
+      <c r="J47" s="28" t="n"/>
+      <c r="K47" s="28" t="n"/>
+      <c r="L47" s="28" t="n"/>
+      <c r="M47" s="28" t="n"/>
+      <c r="N47" s="28" t="n"/>
+      <c r="O47" s="28" t="n"/>
+      <c r="P47" s="28" t="n"/>
+      <c r="Q47" s="28" t="n"/>
+      <c r="R47" s="28" t="n"/>
     </row>
     <row r="48">
-      <c r="A48" s="28" t="n"/>
-      <c r="B48" s="28" t="n"/>
-      <c r="C48" s="28" t="n"/>
-      <c r="D48" s="28" t="n"/>
-      <c r="E48" s="28" t="n"/>
-      <c r="F48" s="28" t="n"/>
-      <c r="G48" s="28" t="n"/>
-      <c r="H48" s="28" t="n"/>
-      <c r="I48" s="28" t="n"/>
-      <c r="J48" s="28" t="n"/>
-      <c r="K48" s="28" t="n"/>
-      <c r="L48" s="28" t="n"/>
-      <c r="M48" s="28" t="n"/>
-      <c r="N48" s="28" t="n"/>
-      <c r="O48" s="28" t="n"/>
-      <c r="P48" s="28" t="n"/>
-      <c r="Q48" s="28" t="n"/>
-      <c r="R48" s="28" t="n"/>
+      <c r="A48" s="29" t="n"/>
+      <c r="B48" s="29" t="n"/>
+      <c r="C48" s="29" t="n"/>
+      <c r="D48" s="29" t="n"/>
+      <c r="E48" s="29" t="n"/>
+      <c r="F48" s="29" t="n"/>
+      <c r="G48" s="29" t="n"/>
+      <c r="H48" s="29" t="n"/>
+      <c r="I48" s="29" t="n"/>
+      <c r="J48" s="29" t="n"/>
+      <c r="K48" s="29" t="n"/>
+      <c r="L48" s="29" t="n"/>
+      <c r="M48" s="29" t="n"/>
+      <c r="N48" s="29" t="n"/>
+      <c r="O48" s="29" t="n"/>
+      <c r="P48" s="29" t="n"/>
+      <c r="Q48" s="29" t="n"/>
+      <c r="R48" s="29" t="n"/>
     </row>
     <row r="49">
-      <c r="A49" s="27" t="n"/>
-      <c r="B49" s="27" t="n"/>
-      <c r="C49" s="27" t="n"/>
-      <c r="D49" s="27" t="n"/>
-      <c r="E49" s="27" t="n"/>
-      <c r="F49" s="27" t="n"/>
-      <c r="G49" s="27" t="n"/>
-      <c r="H49" s="27" t="n"/>
-      <c r="I49" s="27" t="n"/>
-      <c r="J49" s="27" t="n"/>
-      <c r="K49" s="27" t="n"/>
-      <c r="L49" s="27" t="n"/>
-      <c r="M49" s="27" t="n"/>
-      <c r="N49" s="27" t="n"/>
-      <c r="O49" s="27" t="n"/>
-      <c r="P49" s="27" t="n"/>
-      <c r="Q49" s="27" t="n"/>
-      <c r="R49" s="27" t="n"/>
+      <c r="A49" s="28" t="n"/>
+      <c r="B49" s="28" t="n"/>
+      <c r="C49" s="28" t="n"/>
+      <c r="D49" s="28" t="n"/>
+      <c r="E49" s="28" t="n"/>
+      <c r="F49" s="28" t="n"/>
+      <c r="G49" s="28" t="n"/>
+      <c r="H49" s="28" t="n"/>
+      <c r="I49" s="28" t="n"/>
+      <c r="J49" s="28" t="n"/>
+      <c r="K49" s="28" t="n"/>
+      <c r="L49" s="28" t="n"/>
+      <c r="M49" s="28" t="n"/>
+      <c r="N49" s="28" t="n"/>
+      <c r="O49" s="28" t="n"/>
+      <c r="P49" s="28" t="n"/>
+      <c r="Q49" s="28" t="n"/>
+      <c r="R49" s="28" t="n"/>
     </row>
     <row r="50">
-      <c r="A50" s="28" t="n"/>
-      <c r="B50" s="28" t="n"/>
-      <c r="C50" s="28" t="n"/>
-      <c r="D50" s="28" t="n"/>
-      <c r="E50" s="28" t="n"/>
-      <c r="F50" s="28" t="n"/>
-      <c r="G50" s="28" t="n"/>
-      <c r="H50" s="28" t="n"/>
-      <c r="I50" s="28" t="n"/>
-      <c r="J50" s="28" t="n"/>
-      <c r="K50" s="28" t="n"/>
-      <c r="L50" s="28" t="n"/>
-      <c r="M50" s="28" t="n"/>
-      <c r="N50" s="28" t="n"/>
-      <c r="O50" s="28" t="n"/>
-      <c r="P50" s="28" t="n"/>
-      <c r="Q50" s="28" t="n"/>
-      <c r="R50" s="28" t="n"/>
+      <c r="A50" s="29" t="n"/>
+      <c r="B50" s="29" t="n"/>
+      <c r="C50" s="29" t="n"/>
+      <c r="D50" s="29" t="n"/>
+      <c r="E50" s="29" t="n"/>
+      <c r="F50" s="29" t="n"/>
+      <c r="G50" s="29" t="n"/>
+      <c r="H50" s="29" t="n"/>
+      <c r="I50" s="29" t="n"/>
+      <c r="J50" s="29" t="n"/>
+      <c r="K50" s="29" t="n"/>
+      <c r="L50" s="29" t="n"/>
+      <c r="M50" s="29" t="n"/>
+      <c r="N50" s="29" t="n"/>
+      <c r="O50" s="29" t="n"/>
+      <c r="P50" s="29" t="n"/>
+      <c r="Q50" s="29" t="n"/>
+      <c r="R50" s="29" t="n"/>
     </row>
     <row r="51">
-      <c r="A51" s="27" t="n"/>
-      <c r="B51" s="27" t="n"/>
-      <c r="C51" s="27" t="n"/>
-      <c r="D51" s="27" t="n"/>
-      <c r="E51" s="27" t="n"/>
-      <c r="F51" s="27" t="n"/>
-      <c r="G51" s="27" t="n"/>
-      <c r="H51" s="27" t="n"/>
-      <c r="I51" s="27" t="n"/>
-      <c r="J51" s="27" t="n"/>
-      <c r="K51" s="27" t="n"/>
-      <c r="L51" s="27" t="n"/>
-      <c r="M51" s="27" t="n"/>
-      <c r="N51" s="27" t="n"/>
-      <c r="O51" s="27" t="n"/>
-      <c r="P51" s="27" t="n"/>
-      <c r="Q51" s="27" t="n"/>
-      <c r="R51" s="27" t="n"/>
+      <c r="A51" s="28" t="n"/>
+      <c r="B51" s="28" t="n"/>
+      <c r="C51" s="28" t="n"/>
+      <c r="D51" s="28" t="n"/>
+      <c r="E51" s="28" t="n"/>
+      <c r="F51" s="28" t="n"/>
+      <c r="G51" s="28" t="n"/>
+      <c r="H51" s="28" t="n"/>
+      <c r="I51" s="28" t="n"/>
+      <c r="J51" s="28" t="n"/>
+      <c r="K51" s="28" t="n"/>
+      <c r="L51" s="28" t="n"/>
+      <c r="M51" s="28" t="n"/>
+      <c r="N51" s="28" t="n"/>
+      <c r="O51" s="28" t="n"/>
+      <c r="P51" s="28" t="n"/>
+      <c r="Q51" s="28" t="n"/>
+      <c r="R51" s="28" t="n"/>
     </row>
     <row r="52">
-      <c r="A52" s="28" t="n"/>
-      <c r="B52" s="28" t="n"/>
-      <c r="C52" s="28" t="n"/>
-      <c r="D52" s="28" t="n"/>
-      <c r="E52" s="28" t="n"/>
-      <c r="F52" s="28" t="n"/>
-      <c r="G52" s="28" t="n"/>
-      <c r="H52" s="28" t="n"/>
-      <c r="I52" s="28" t="n"/>
-      <c r="J52" s="28" t="n"/>
-      <c r="K52" s="28" t="n"/>
-      <c r="L52" s="28" t="n"/>
-      <c r="M52" s="28" t="n"/>
-      <c r="N52" s="28" t="n"/>
-      <c r="O52" s="28" t="n"/>
-      <c r="P52" s="28" t="n"/>
-      <c r="Q52" s="28" t="n"/>
-      <c r="R52" s="28" t="n"/>
+      <c r="A52" s="29" t="n"/>
+      <c r="B52" s="29" t="n"/>
+      <c r="C52" s="29" t="n"/>
+      <c r="D52" s="29" t="n"/>
+      <c r="E52" s="29" t="n"/>
+      <c r="F52" s="29" t="n"/>
+      <c r="G52" s="29" t="n"/>
+      <c r="H52" s="29" t="n"/>
+      <c r="I52" s="29" t="n"/>
+      <c r="J52" s="29" t="n"/>
+      <c r="K52" s="29" t="n"/>
+      <c r="L52" s="29" t="n"/>
+      <c r="M52" s="29" t="n"/>
+      <c r="N52" s="29" t="n"/>
+      <c r="O52" s="29" t="n"/>
+      <c r="P52" s="29" t="n"/>
+      <c r="Q52" s="29" t="n"/>
+      <c r="R52" s="29" t="n"/>
     </row>
     <row r="53">
-      <c r="A53" s="27" t="n"/>
-      <c r="B53" s="27" t="n"/>
-      <c r="C53" s="27" t="n"/>
-      <c r="D53" s="27" t="n"/>
-      <c r="E53" s="27" t="n"/>
-      <c r="F53" s="27" t="n"/>
-      <c r="G53" s="27" t="n"/>
-      <c r="H53" s="27" t="n"/>
-      <c r="I53" s="27" t="n"/>
-      <c r="J53" s="27" t="n"/>
-      <c r="K53" s="27" t="n"/>
-      <c r="L53" s="27" t="n"/>
-      <c r="M53" s="27" t="n"/>
-      <c r="N53" s="27" t="n"/>
-      <c r="O53" s="27" t="n"/>
-      <c r="P53" s="27" t="n"/>
-      <c r="Q53" s="27" t="n"/>
-      <c r="R53" s="27" t="n"/>
+      <c r="A53" s="28" t="n"/>
+      <c r="B53" s="28" t="n"/>
+      <c r="C53" s="28" t="n"/>
+      <c r="D53" s="28" t="n"/>
+      <c r="E53" s="28" t="n"/>
+      <c r="F53" s="28" t="n"/>
+      <c r="G53" s="28" t="n"/>
+      <c r="H53" s="28" t="n"/>
+      <c r="I53" s="28" t="n"/>
+      <c r="J53" s="28" t="n"/>
+      <c r="K53" s="28" t="n"/>
+      <c r="L53" s="28" t="n"/>
+      <c r="M53" s="28" t="n"/>
+      <c r="N53" s="28" t="n"/>
+      <c r="O53" s="28" t="n"/>
+      <c r="P53" s="28" t="n"/>
+      <c r="Q53" s="28" t="n"/>
+      <c r="R53" s="28" t="n"/>
     </row>
     <row r="54">
-      <c r="A54" s="28" t="n"/>
-      <c r="B54" s="28" t="n"/>
-      <c r="C54" s="28" t="n"/>
-      <c r="D54" s="28" t="n"/>
-      <c r="E54" s="28" t="n"/>
-      <c r="F54" s="28" t="n"/>
-      <c r="G54" s="28" t="n"/>
-      <c r="H54" s="28" t="n"/>
-      <c r="I54" s="28" t="n"/>
-      <c r="J54" s="28" t="n"/>
-      <c r="K54" s="28" t="n"/>
-      <c r="L54" s="28" t="n"/>
-      <c r="M54" s="28" t="n"/>
-      <c r="N54" s="28" t="n"/>
-      <c r="O54" s="28" t="n"/>
-      <c r="P54" s="28" t="n"/>
-      <c r="Q54" s="28" t="n"/>
-      <c r="R54" s="28" t="n"/>
+      <c r="A54" s="29" t="n"/>
+      <c r="B54" s="29" t="n"/>
+      <c r="C54" s="29" t="n"/>
+      <c r="D54" s="29" t="n"/>
+      <c r="E54" s="29" t="n"/>
+      <c r="F54" s="29" t="n"/>
+      <c r="G54" s="29" t="n"/>
+      <c r="H54" s="29" t="n"/>
+      <c r="I54" s="29" t="n"/>
+      <c r="J54" s="29" t="n"/>
+      <c r="K54" s="29" t="n"/>
+      <c r="L54" s="29" t="n"/>
+      <c r="M54" s="29" t="n"/>
+      <c r="N54" s="29" t="n"/>
+      <c r="O54" s="29" t="n"/>
+      <c r="P54" s="29" t="n"/>
+      <c r="Q54" s="29" t="n"/>
+      <c r="R54" s="29" t="n"/>
     </row>
     <row r="55">
-      <c r="A55" s="27" t="n"/>
-      <c r="B55" s="27" t="n"/>
-      <c r="C55" s="27" t="n"/>
-      <c r="D55" s="27" t="n"/>
-      <c r="E55" s="27" t="n"/>
-      <c r="F55" s="27" t="n"/>
-      <c r="G55" s="27" t="n"/>
-      <c r="H55" s="27" t="n"/>
-      <c r="I55" s="27" t="n"/>
-      <c r="J55" s="27" t="n"/>
-      <c r="K55" s="27" t="n"/>
-      <c r="L55" s="27" t="n"/>
-      <c r="M55" s="27" t="n"/>
-      <c r="N55" s="27" t="n"/>
-      <c r="O55" s="27" t="n"/>
-      <c r="P55" s="27" t="n"/>
-      <c r="Q55" s="27" t="n"/>
-      <c r="R55" s="27" t="n"/>
+      <c r="A55" s="28" t="n"/>
+      <c r="B55" s="28" t="n"/>
+      <c r="C55" s="28" t="n"/>
+      <c r="D55" s="28" t="n"/>
+      <c r="E55" s="28" t="n"/>
+      <c r="F55" s="28" t="n"/>
+      <c r="G55" s="28" t="n"/>
+      <c r="H55" s="28" t="n"/>
+      <c r="I55" s="28" t="n"/>
+      <c r="J55" s="28" t="n"/>
+      <c r="K55" s="28" t="n"/>
+      <c r="L55" s="28" t="n"/>
+      <c r="M55" s="28" t="n"/>
+      <c r="N55" s="28" t="n"/>
+      <c r="O55" s="28" t="n"/>
+      <c r="P55" s="28" t="n"/>
+      <c r="Q55" s="28" t="n"/>
+      <c r="R55" s="28" t="n"/>
     </row>
     <row r="56">
-      <c r="A56" s="28" t="n"/>
-      <c r="B56" s="28" t="n"/>
-      <c r="C56" s="28" t="n"/>
-      <c r="D56" s="28" t="n"/>
-      <c r="E56" s="28" t="n"/>
-      <c r="F56" s="28" t="n"/>
-      <c r="G56" s="28" t="n"/>
-      <c r="H56" s="28" t="n"/>
-      <c r="I56" s="28" t="n"/>
-      <c r="J56" s="28" t="n"/>
-      <c r="K56" s="28" t="n"/>
-      <c r="L56" s="28" t="n"/>
-      <c r="M56" s="28" t="n"/>
-      <c r="N56" s="28" t="n"/>
-      <c r="O56" s="28" t="n"/>
-      <c r="P56" s="28" t="n"/>
-      <c r="Q56" s="28" t="n"/>
-      <c r="R56" s="28" t="n"/>
+      <c r="A56" s="29" t="n"/>
+      <c r="B56" s="29" t="n"/>
+      <c r="C56" s="29" t="n"/>
+      <c r="D56" s="29" t="n"/>
+      <c r="E56" s="29" t="n"/>
+      <c r="F56" s="29" t="n"/>
+      <c r="G56" s="29" t="n"/>
+      <c r="H56" s="29" t="n"/>
+      <c r="I56" s="29" t="n"/>
+      <c r="J56" s="29" t="n"/>
+      <c r="K56" s="29" t="n"/>
+      <c r="L56" s="29" t="n"/>
+      <c r="M56" s="29" t="n"/>
+      <c r="N56" s="29" t="n"/>
+      <c r="O56" s="29" t="n"/>
+      <c r="P56" s="29" t="n"/>
+      <c r="Q56" s="29" t="n"/>
+      <c r="R56" s="29" t="n"/>
     </row>
     <row r="57">
-      <c r="A57" s="27" t="n"/>
-      <c r="B57" s="27" t="n"/>
-      <c r="C57" s="27" t="n"/>
-      <c r="D57" s="27" t="n"/>
-      <c r="E57" s="27" t="n"/>
-      <c r="F57" s="27" t="n"/>
-      <c r="G57" s="27" t="n"/>
-      <c r="H57" s="27" t="n"/>
-      <c r="I57" s="27" t="n"/>
-      <c r="J57" s="27" t="n"/>
-      <c r="K57" s="27" t="n"/>
-      <c r="L57" s="27" t="n"/>
-      <c r="M57" s="27" t="n"/>
-      <c r="N57" s="27" t="n"/>
-      <c r="O57" s="27" t="n"/>
-      <c r="P57" s="27" t="n"/>
-      <c r="Q57" s="27" t="n"/>
-      <c r="R57" s="27" t="n"/>
+      <c r="A57" s="28" t="n"/>
+      <c r="B57" s="28" t="n"/>
+      <c r="C57" s="28" t="n"/>
+      <c r="D57" s="28" t="n"/>
+      <c r="E57" s="28" t="n"/>
+      <c r="F57" s="28" t="n"/>
+      <c r="G57" s="28" t="n"/>
+      <c r="H57" s="28" t="n"/>
+      <c r="I57" s="28" t="n"/>
+      <c r="J57" s="28" t="n"/>
+      <c r="K57" s="28" t="n"/>
+      <c r="L57" s="28" t="n"/>
+      <c r="M57" s="28" t="n"/>
+      <c r="N57" s="28" t="n"/>
+      <c r="O57" s="28" t="n"/>
+      <c r="P57" s="28" t="n"/>
+      <c r="Q57" s="28" t="n"/>
+      <c r="R57" s="28" t="n"/>
     </row>
     <row r="58">
-      <c r="A58" s="28" t="n"/>
-      <c r="B58" s="28" t="n"/>
-      <c r="C58" s="28" t="n"/>
-      <c r="D58" s="28" t="n"/>
-      <c r="E58" s="28" t="n"/>
-      <c r="F58" s="28" t="n"/>
-      <c r="G58" s="28" t="n"/>
-      <c r="H58" s="28" t="n"/>
-      <c r="I58" s="28" t="n"/>
-      <c r="J58" s="28" t="n"/>
-      <c r="K58" s="28" t="n"/>
-      <c r="L58" s="28" t="n"/>
-      <c r="M58" s="28" t="n"/>
-      <c r="N58" s="28" t="n"/>
-      <c r="O58" s="28" t="n"/>
-      <c r="P58" s="28" t="n"/>
-      <c r="Q58" s="28" t="n"/>
-      <c r="R58" s="28" t="n"/>
+      <c r="A58" s="29" t="n"/>
+      <c r="B58" s="29" t="n"/>
+      <c r="C58" s="29" t="n"/>
+      <c r="D58" s="29" t="n"/>
+      <c r="E58" s="29" t="n"/>
+      <c r="F58" s="29" t="n"/>
+      <c r="G58" s="29" t="n"/>
+      <c r="H58" s="29" t="n"/>
+      <c r="I58" s="29" t="n"/>
+      <c r="J58" s="29" t="n"/>
+      <c r="K58" s="29" t="n"/>
+      <c r="L58" s="29" t="n"/>
+      <c r="M58" s="29" t="n"/>
+      <c r="N58" s="29" t="n"/>
+      <c r="O58" s="29" t="n"/>
+      <c r="P58" s="29" t="n"/>
+      <c r="Q58" s="29" t="n"/>
+      <c r="R58" s="29" t="n"/>
     </row>
     <row r="59">
-      <c r="A59" s="27" t="n"/>
-      <c r="B59" s="27" t="n"/>
-      <c r="C59" s="27" t="n"/>
-      <c r="D59" s="27" t="n"/>
-      <c r="E59" s="27" t="n"/>
-      <c r="F59" s="27" t="n"/>
-      <c r="G59" s="27" t="n"/>
-      <c r="H59" s="27" t="n"/>
-      <c r="I59" s="27" t="n"/>
-      <c r="J59" s="27" t="n"/>
-      <c r="K59" s="27" t="n"/>
-      <c r="L59" s="27" t="n"/>
-      <c r="M59" s="27" t="n"/>
-      <c r="N59" s="27" t="n"/>
-      <c r="O59" s="27" t="n"/>
-      <c r="P59" s="27" t="n"/>
-      <c r="Q59" s="27" t="n"/>
-      <c r="R59" s="27" t="n"/>
+      <c r="A59" s="28" t="n"/>
+      <c r="B59" s="28" t="n"/>
+      <c r="C59" s="28" t="n"/>
+      <c r="D59" s="28" t="n"/>
+      <c r="E59" s="28" t="n"/>
+      <c r="F59" s="28" t="n"/>
+      <c r="G59" s="28" t="n"/>
+      <c r="H59" s="28" t="n"/>
+      <c r="I59" s="28" t="n"/>
+      <c r="J59" s="28" t="n"/>
+      <c r="K59" s="28" t="n"/>
+      <c r="L59" s="28" t="n"/>
+      <c r="M59" s="28" t="n"/>
+      <c r="N59" s="28" t="n"/>
+      <c r="O59" s="28" t="n"/>
+      <c r="P59" s="28" t="n"/>
+      <c r="Q59" s="28" t="n"/>
+      <c r="R59" s="28" t="n"/>
     </row>
     <row r="60">
-      <c r="A60" s="28" t="n"/>
-      <c r="B60" s="28" t="n"/>
-      <c r="C60" s="28" t="n"/>
-      <c r="D60" s="28" t="n"/>
-      <c r="E60" s="28" t="n"/>
-      <c r="F60" s="28" t="n"/>
-      <c r="G60" s="28" t="n"/>
-      <c r="H60" s="28" t="n"/>
-      <c r="I60" s="28" t="n"/>
-      <c r="J60" s="28" t="n"/>
-      <c r="K60" s="28" t="n"/>
-      <c r="L60" s="28" t="n"/>
-      <c r="M60" s="28" t="n"/>
-      <c r="N60" s="28" t="n"/>
-      <c r="O60" s="28" t="n"/>
-      <c r="P60" s="28" t="n"/>
-      <c r="Q60" s="28" t="n"/>
-      <c r="R60" s="28" t="n"/>
+      <c r="A60" s="29" t="n"/>
+      <c r="B60" s="29" t="n"/>
+      <c r="C60" s="29" t="n"/>
+      <c r="D60" s="29" t="n"/>
+      <c r="E60" s="29" t="n"/>
+      <c r="F60" s="29" t="n"/>
+      <c r="G60" s="29" t="n"/>
+      <c r="H60" s="29" t="n"/>
+      <c r="I60" s="29" t="n"/>
+      <c r="J60" s="29" t="n"/>
+      <c r="K60" s="29" t="n"/>
+      <c r="L60" s="29" t="n"/>
+      <c r="M60" s="29" t="n"/>
+      <c r="N60" s="29" t="n"/>
+      <c r="O60" s="29" t="n"/>
+      <c r="P60" s="29" t="n"/>
+      <c r="Q60" s="29" t="n"/>
+      <c r="R60" s="29" t="n"/>
     </row>
     <row r="61">
-      <c r="A61" s="27" t="n"/>
-      <c r="B61" s="27" t="n"/>
-      <c r="C61" s="27" t="n"/>
-      <c r="D61" s="27" t="n"/>
-      <c r="E61" s="27" t="n"/>
-      <c r="F61" s="27" t="n"/>
-      <c r="G61" s="27" t="n"/>
-      <c r="H61" s="27" t="n"/>
-      <c r="I61" s="27" t="n"/>
-      <c r="J61" s="27" t="n"/>
-      <c r="K61" s="27" t="n"/>
-      <c r="L61" s="27" t="n"/>
-      <c r="M61" s="27" t="n"/>
-      <c r="N61" s="27" t="n"/>
-      <c r="O61" s="27" t="n"/>
-      <c r="P61" s="27" t="n"/>
-      <c r="Q61" s="27" t="n"/>
-      <c r="R61" s="27" t="n"/>
+      <c r="A61" s="28" t="n"/>
+      <c r="B61" s="28" t="n"/>
+      <c r="C61" s="28" t="n"/>
+      <c r="D61" s="28" t="n"/>
+      <c r="E61" s="28" t="n"/>
+      <c r="F61" s="28" t="n"/>
+      <c r="G61" s="28" t="n"/>
+      <c r="H61" s="28" t="n"/>
+      <c r="I61" s="28" t="n"/>
+      <c r="J61" s="28" t="n"/>
+      <c r="K61" s="28" t="n"/>
+      <c r="L61" s="28" t="n"/>
+      <c r="M61" s="28" t="n"/>
+      <c r="N61" s="28" t="n"/>
+      <c r="O61" s="28" t="n"/>
+      <c r="P61" s="28" t="n"/>
+      <c r="Q61" s="28" t="n"/>
+      <c r="R61" s="28" t="n"/>
     </row>
     <row r="62">
-      <c r="A62" s="28" t="n"/>
-      <c r="B62" s="28" t="n"/>
-      <c r="C62" s="28" t="n"/>
-      <c r="D62" s="28" t="n"/>
-      <c r="E62" s="28" t="n"/>
-      <c r="F62" s="28" t="n"/>
-      <c r="G62" s="28" t="n"/>
-      <c r="H62" s="28" t="n"/>
-      <c r="I62" s="28" t="n"/>
-      <c r="J62" s="28" t="n"/>
-      <c r="K62" s="28" t="n"/>
-      <c r="L62" s="28" t="n"/>
-      <c r="M62" s="28" t="n"/>
-      <c r="N62" s="28" t="n"/>
-      <c r="O62" s="28" t="n"/>
-      <c r="P62" s="28" t="n"/>
-      <c r="Q62" s="28" t="n"/>
-      <c r="R62" s="28" t="n"/>
+      <c r="A62" s="29" t="n"/>
+      <c r="B62" s="29" t="n"/>
+      <c r="C62" s="29" t="n"/>
+      <c r="D62" s="29" t="n"/>
+      <c r="E62" s="29" t="n"/>
+      <c r="F62" s="29" t="n"/>
+      <c r="G62" s="29" t="n"/>
+      <c r="H62" s="29" t="n"/>
+      <c r="I62" s="29" t="n"/>
+      <c r="J62" s="29" t="n"/>
+      <c r="K62" s="29" t="n"/>
+      <c r="L62" s="29" t="n"/>
+      <c r="M62" s="29" t="n"/>
+      <c r="N62" s="29" t="n"/>
+      <c r="O62" s="29" t="n"/>
+      <c r="P62" s="29" t="n"/>
+      <c r="Q62" s="29" t="n"/>
+      <c r="R62" s="29" t="n"/>
     </row>
     <row r="63">
-      <c r="A63" s="27" t="n"/>
-      <c r="B63" s="27" t="n"/>
-      <c r="C63" s="27" t="n"/>
-      <c r="D63" s="27" t="n"/>
-      <c r="E63" s="27" t="n"/>
-      <c r="F63" s="27" t="n"/>
-      <c r="G63" s="27" t="n"/>
-      <c r="H63" s="27" t="n"/>
-      <c r="I63" s="27" t="n"/>
-      <c r="J63" s="27" t="n"/>
-      <c r="K63" s="27" t="n"/>
-      <c r="L63" s="27" t="n"/>
-      <c r="M63" s="27" t="n"/>
-      <c r="N63" s="27" t="n"/>
-      <c r="O63" s="27" t="n"/>
-      <c r="P63" s="27" t="n"/>
-      <c r="Q63" s="27" t="n"/>
-      <c r="R63" s="27" t="n"/>
+      <c r="A63" s="28" t="n"/>
+      <c r="B63" s="28" t="n"/>
+      <c r="C63" s="28" t="n"/>
+      <c r="D63" s="28" t="n"/>
+      <c r="E63" s="28" t="n"/>
+      <c r="F63" s="28" t="n"/>
+      <c r="G63" s="28" t="n"/>
+      <c r="H63" s="28" t="n"/>
+      <c r="I63" s="28" t="n"/>
+      <c r="J63" s="28" t="n"/>
+      <c r="K63" s="28" t="n"/>
+      <c r="L63" s="28" t="n"/>
+      <c r="M63" s="28" t="n"/>
+      <c r="N63" s="28" t="n"/>
+      <c r="O63" s="28" t="n"/>
+      <c r="P63" s="28" t="n"/>
+      <c r="Q63" s="28" t="n"/>
+      <c r="R63" s="28" t="n"/>
     </row>
     <row r="64">
-      <c r="A64" s="28" t="n"/>
-      <c r="B64" s="28" t="n"/>
-      <c r="C64" s="28" t="n"/>
-      <c r="D64" s="28" t="n"/>
-      <c r="E64" s="28" t="n"/>
-      <c r="F64" s="28" t="n"/>
-      <c r="G64" s="28" t="n"/>
-      <c r="H64" s="28" t="n"/>
-      <c r="I64" s="28" t="n"/>
-      <c r="J64" s="28" t="n"/>
-      <c r="K64" s="28" t="n"/>
-      <c r="L64" s="28" t="n"/>
-      <c r="M64" s="28" t="n"/>
-      <c r="N64" s="28" t="n"/>
-      <c r="O64" s="28" t="n"/>
-      <c r="P64" s="28" t="n"/>
-      <c r="Q64" s="28" t="n"/>
-      <c r="R64" s="28" t="n"/>
+      <c r="A64" s="29" t="n"/>
+      <c r="B64" s="29" t="n"/>
+      <c r="C64" s="29" t="n"/>
+      <c r="D64" s="29" t="n"/>
+      <c r="E64" s="29" t="n"/>
+      <c r="F64" s="29" t="n"/>
+      <c r="G64" s="29" t="n"/>
+      <c r="H64" s="29" t="n"/>
+      <c r="I64" s="29" t="n"/>
+      <c r="J64" s="29" t="n"/>
+      <c r="K64" s="29" t="n"/>
+      <c r="L64" s="29" t="n"/>
+      <c r="M64" s="29" t="n"/>
+      <c r="N64" s="29" t="n"/>
+      <c r="O64" s="29" t="n"/>
+      <c r="P64" s="29" t="n"/>
+      <c r="Q64" s="29" t="n"/>
+      <c r="R64" s="29" t="n"/>
     </row>
     <row r="65">
-      <c r="A65" s="27" t="n"/>
-      <c r="B65" s="27" t="n"/>
-      <c r="C65" s="27" t="n"/>
-      <c r="D65" s="27" t="n"/>
-      <c r="E65" s="27" t="n"/>
-      <c r="F65" s="27" t="n"/>
-      <c r="G65" s="27" t="n"/>
-      <c r="H65" s="27" t="n"/>
-      <c r="I65" s="27" t="n"/>
-      <c r="J65" s="27" t="n"/>
-      <c r="K65" s="27" t="n"/>
-      <c r="L65" s="27" t="n"/>
-      <c r="M65" s="27" t="n"/>
-      <c r="N65" s="27" t="n"/>
-      <c r="O65" s="27" t="n"/>
-      <c r="P65" s="27" t="n"/>
-      <c r="Q65" s="27" t="n"/>
-      <c r="R65" s="27" t="n"/>
+      <c r="A65" s="28" t="n"/>
+      <c r="B65" s="28" t="n"/>
+      <c r="C65" s="28" t="n"/>
+      <c r="D65" s="28" t="n"/>
+      <c r="E65" s="28" t="n"/>
+      <c r="F65" s="28" t="n"/>
+      <c r="G65" s="28" t="n"/>
+      <c r="H65" s="28" t="n"/>
+      <c r="I65" s="28" t="n"/>
+      <c r="J65" s="28" t="n"/>
+      <c r="K65" s="28" t="n"/>
+      <c r="L65" s="28" t="n"/>
+      <c r="M65" s="28" t="n"/>
+      <c r="N65" s="28" t="n"/>
+      <c r="O65" s="28" t="n"/>
+      <c r="P65" s="28" t="n"/>
+      <c r="Q65" s="28" t="n"/>
+      <c r="R65" s="28" t="n"/>
     </row>
     <row r="66">
-      <c r="A66" s="28" t="n"/>
-      <c r="B66" s="28" t="n"/>
-      <c r="C66" s="28" t="n"/>
-      <c r="D66" s="28" t="n"/>
-      <c r="E66" s="28" t="n"/>
-      <c r="F66" s="28" t="n"/>
-      <c r="G66" s="28" t="n"/>
-      <c r="H66" s="28" t="n"/>
-      <c r="I66" s="28" t="n"/>
-      <c r="J66" s="28" t="n"/>
-      <c r="K66" s="28" t="n"/>
-      <c r="L66" s="28" t="n"/>
-      <c r="M66" s="28" t="n"/>
-      <c r="N66" s="28" t="n"/>
-      <c r="O66" s="28" t="n"/>
-      <c r="P66" s="28" t="n"/>
-      <c r="Q66" s="28" t="n"/>
-      <c r="R66" s="28" t="n"/>
+      <c r="A66" s="29" t="n"/>
+      <c r="B66" s="29" t="n"/>
+      <c r="C66" s="29" t="n"/>
+      <c r="D66" s="29" t="n"/>
+      <c r="E66" s="29" t="n"/>
+      <c r="F66" s="29" t="n"/>
+      <c r="G66" s="29" t="n"/>
+      <c r="H66" s="29" t="n"/>
+      <c r="I66" s="29" t="n"/>
+      <c r="J66" s="29" t="n"/>
+      <c r="K66" s="29" t="n"/>
+      <c r="L66" s="29" t="n"/>
+      <c r="M66" s="29" t="n"/>
+      <c r="N66" s="29" t="n"/>
+      <c r="O66" s="29" t="n"/>
+      <c r="P66" s="29" t="n"/>
+      <c r="Q66" s="29" t="n"/>
+      <c r="R66" s="29" t="n"/>
     </row>
     <row r="67">
-      <c r="A67" s="27" t="n"/>
-      <c r="B67" s="27" t="n"/>
-      <c r="C67" s="27" t="n"/>
-      <c r="D67" s="27" t="n"/>
-      <c r="E67" s="27" t="n"/>
-      <c r="F67" s="27" t="n"/>
-      <c r="G67" s="27" t="n"/>
-      <c r="H67" s="27" t="n"/>
-      <c r="I67" s="27" t="n"/>
-      <c r="J67" s="27" t="n"/>
-      <c r="K67" s="27" t="n"/>
-      <c r="L67" s="27" t="n"/>
-      <c r="M67" s="27" t="n"/>
-      <c r="N67" s="27" t="n"/>
-      <c r="O67" s="27" t="n"/>
-      <c r="P67" s="27" t="n"/>
-      <c r="Q67" s="27" t="n"/>
-      <c r="R67" s="27" t="n"/>
+      <c r="A67" s="28" t="n"/>
+      <c r="B67" s="28" t="n"/>
+      <c r="C67" s="28" t="n"/>
+      <c r="D67" s="28" t="n"/>
+      <c r="E67" s="28" t="n"/>
+      <c r="F67" s="28" t="n"/>
+      <c r="G67" s="28" t="n"/>
+      <c r="H67" s="28" t="n"/>
+      <c r="I67" s="28" t="n"/>
+      <c r="J67" s="28" t="n"/>
+      <c r="K67" s="28" t="n"/>
+      <c r="L67" s="28" t="n"/>
+      <c r="M67" s="28" t="n"/>
+      <c r="N67" s="28" t="n"/>
+      <c r="O67" s="28" t="n"/>
+      <c r="P67" s="28" t="n"/>
+      <c r="Q67" s="28" t="n"/>
+      <c r="R67" s="28" t="n"/>
     </row>
     <row r="68">
-      <c r="A68" s="28" t="n"/>
-      <c r="B68" s="28" t="n"/>
-      <c r="C68" s="28" t="n"/>
-      <c r="D68" s="28" t="n"/>
-      <c r="E68" s="28" t="n"/>
-      <c r="F68" s="28" t="n"/>
-      <c r="G68" s="28" t="n"/>
-      <c r="H68" s="28" t="n"/>
-      <c r="I68" s="28" t="n"/>
-      <c r="J68" s="28" t="n"/>
-      <c r="K68" s="28" t="n"/>
-      <c r="L68" s="28" t="n"/>
-      <c r="M68" s="28" t="n"/>
-      <c r="N68" s="28" t="n"/>
-      <c r="O68" s="28" t="n"/>
-      <c r="P68" s="28" t="n"/>
-      <c r="Q68" s="28" t="n"/>
-      <c r="R68" s="28" t="n"/>
+      <c r="A68" s="29" t="n"/>
+      <c r="B68" s="29" t="n"/>
+      <c r="C68" s="29" t="n"/>
+      <c r="D68" s="29" t="n"/>
+      <c r="E68" s="29" t="n"/>
+      <c r="F68" s="29" t="n"/>
+      <c r="G68" s="29" t="n"/>
+      <c r="H68" s="29" t="n"/>
+      <c r="I68" s="29" t="n"/>
+      <c r="J68" s="29" t="n"/>
+      <c r="K68" s="29" t="n"/>
+      <c r="L68" s="29" t="n"/>
+      <c r="M68" s="29" t="n"/>
+      <c r="N68" s="29" t="n"/>
+      <c r="O68" s="29" t="n"/>
+      <c r="P68" s="29" t="n"/>
+      <c r="Q68" s="29" t="n"/>
+      <c r="R68" s="29" t="n"/>
     </row>
     <row r="69">
-      <c r="A69" s="27" t="n"/>
-      <c r="B69" s="27" t="n"/>
-      <c r="C69" s="27" t="n"/>
-      <c r="D69" s="27" t="n"/>
-      <c r="E69" s="27" t="n"/>
-      <c r="F69" s="27" t="n"/>
-      <c r="G69" s="27" t="n"/>
-      <c r="H69" s="27" t="n"/>
-      <c r="I69" s="27" t="n"/>
-      <c r="J69" s="27" t="n"/>
-      <c r="K69" s="27" t="n"/>
-      <c r="L69" s="27" t="n"/>
-      <c r="M69" s="27" t="n"/>
-      <c r="N69" s="27" t="n"/>
-      <c r="O69" s="27" t="n"/>
-      <c r="P69" s="27" t="n"/>
-      <c r="Q69" s="27" t="n"/>
-      <c r="R69" s="27" t="n"/>
+      <c r="A69" s="28" t="n"/>
+      <c r="B69" s="28" t="n"/>
+      <c r="C69" s="28" t="n"/>
+      <c r="D69" s="28" t="n"/>
+      <c r="E69" s="28" t="n"/>
+      <c r="F69" s="28" t="n"/>
+      <c r="G69" s="28" t="n"/>
+      <c r="H69" s="28" t="n"/>
+      <c r="I69" s="28" t="n"/>
+      <c r="J69" s="28" t="n"/>
+      <c r="K69" s="28" t="n"/>
+      <c r="L69" s="28" t="n"/>
+      <c r="M69" s="28" t="n"/>
+      <c r="N69" s="28" t="n"/>
+      <c r="O69" s="28" t="n"/>
+      <c r="P69" s="28" t="n"/>
+      <c r="Q69" s="28" t="n"/>
+      <c r="R69" s="28" t="n"/>
     </row>
     <row r="70">
-      <c r="A70" s="28" t="n"/>
-      <c r="B70" s="28" t="n"/>
-      <c r="C70" s="28" t="n"/>
-      <c r="D70" s="28" t="n"/>
-      <c r="E70" s="28" t="n"/>
-      <c r="F70" s="28" t="n"/>
-      <c r="G70" s="28" t="n"/>
-      <c r="H70" s="28" t="n"/>
-      <c r="I70" s="28" t="n"/>
-      <c r="J70" s="28" t="n"/>
-      <c r="K70" s="28" t="n"/>
-      <c r="L70" s="28" t="n"/>
-      <c r="M70" s="28" t="n"/>
-      <c r="N70" s="28" t="n"/>
-      <c r="O70" s="28" t="n"/>
-      <c r="P70" s="28" t="n"/>
-      <c r="Q70" s="28" t="n"/>
-      <c r="R70" s="28" t="n"/>
+      <c r="A70" s="29" t="n"/>
+      <c r="B70" s="29" t="n"/>
+      <c r="C70" s="29" t="n"/>
+      <c r="D70" s="29" t="n"/>
+      <c r="E70" s="29" t="n"/>
+      <c r="F70" s="29" t="n"/>
+      <c r="G70" s="29" t="n"/>
+      <c r="H70" s="29" t="n"/>
+      <c r="I70" s="29" t="n"/>
+      <c r="J70" s="29" t="n"/>
+      <c r="K70" s="29" t="n"/>
+      <c r="L70" s="29" t="n"/>
+      <c r="M70" s="29" t="n"/>
+      <c r="N70" s="29" t="n"/>
+      <c r="O70" s="29" t="n"/>
+      <c r="P70" s="29" t="n"/>
+      <c r="Q70" s="29" t="n"/>
+      <c r="R70" s="29" t="n"/>
     </row>
     <row r="71">
-      <c r="A71" s="27" t="n"/>
-      <c r="B71" s="27" t="n"/>
-      <c r="C71" s="27" t="n"/>
-      <c r="D71" s="27" t="n"/>
-      <c r="E71" s="27" t="n"/>
-      <c r="F71" s="27" t="n"/>
-      <c r="G71" s="27" t="n"/>
-      <c r="H71" s="27" t="n"/>
-      <c r="I71" s="27" t="n"/>
-      <c r="J71" s="27" t="n"/>
-      <c r="K71" s="27" t="n"/>
-      <c r="L71" s="27" t="n"/>
-      <c r="M71" s="27" t="n"/>
-      <c r="N71" s="27" t="n"/>
-      <c r="O71" s="27" t="n"/>
-      <c r="P71" s="27" t="n"/>
-      <c r="Q71" s="27" t="n"/>
-      <c r="R71" s="27" t="n"/>
+      <c r="A71" s="28" t="n"/>
+      <c r="B71" s="28" t="n"/>
+      <c r="C71" s="28" t="n"/>
+      <c r="D71" s="28" t="n"/>
+      <c r="E71" s="28" t="n"/>
+      <c r="F71" s="28" t="n"/>
+      <c r="G71" s="28" t="n"/>
+      <c r="H71" s="28" t="n"/>
+      <c r="I71" s="28" t="n"/>
+      <c r="J71" s="28" t="n"/>
+      <c r="K71" s="28" t="n"/>
+      <c r="L71" s="28" t="n"/>
+      <c r="M71" s="28" t="n"/>
+      <c r="N71" s="28" t="n"/>
+      <c r="O71" s="28" t="n"/>
+      <c r="P71" s="28" t="n"/>
+      <c r="Q71" s="28" t="n"/>
+      <c r="R71" s="28" t="n"/>
     </row>
     <row r="72">
-      <c r="A72" s="28" t="n"/>
-      <c r="B72" s="28" t="n"/>
-      <c r="C72" s="28" t="n"/>
-      <c r="D72" s="28" t="n"/>
-      <c r="E72" s="28" t="n"/>
-      <c r="F72" s="28" t="n"/>
-      <c r="G72" s="28" t="n"/>
-      <c r="H72" s="28" t="n"/>
-      <c r="I72" s="28" t="n"/>
-      <c r="J72" s="28" t="n"/>
-      <c r="K72" s="28" t="n"/>
-      <c r="L72" s="28" t="n"/>
-      <c r="M72" s="28" t="n"/>
-      <c r="N72" s="28" t="n"/>
-      <c r="O72" s="28" t="n"/>
-      <c r="P72" s="28" t="n"/>
-      <c r="Q72" s="28" t="n"/>
-      <c r="R72" s="28" t="n"/>
+      <c r="A72" s="29" t="n"/>
+      <c r="B72" s="29" t="n"/>
+      <c r="C72" s="29" t="n"/>
+      <c r="D72" s="29" t="n"/>
+      <c r="E72" s="29" t="n"/>
+      <c r="F72" s="29" t="n"/>
+      <c r="G72" s="29" t="n"/>
+      <c r="H72" s="29" t="n"/>
+      <c r="I72" s="29" t="n"/>
+      <c r="J72" s="29" t="n"/>
+      <c r="K72" s="29" t="n"/>
+      <c r="L72" s="29" t="n"/>
+      <c r="M72" s="29" t="n"/>
+      <c r="N72" s="29" t="n"/>
+      <c r="O72" s="29" t="n"/>
+      <c r="P72" s="29" t="n"/>
+      <c r="Q72" s="29" t="n"/>
+      <c r="R72" s="29" t="n"/>
     </row>
     <row r="73">
-      <c r="A73" s="27" t="n"/>
-      <c r="B73" s="27" t="n"/>
-      <c r="C73" s="27" t="n"/>
-      <c r="D73" s="27" t="n"/>
-      <c r="E73" s="27" t="n"/>
-      <c r="F73" s="27" t="n"/>
-      <c r="G73" s="27" t="n"/>
-      <c r="H73" s="27" t="n"/>
-      <c r="I73" s="27" t="n"/>
-      <c r="J73" s="27" t="n"/>
-      <c r="K73" s="27" t="n"/>
-      <c r="L73" s="27" t="n"/>
-      <c r="M73" s="27" t="n"/>
-      <c r="N73" s="27" t="n"/>
-      <c r="O73" s="27" t="n"/>
-      <c r="P73" s="27" t="n"/>
-      <c r="Q73" s="27" t="n"/>
-      <c r="R73" s="27" t="n"/>
+      <c r="A73" s="28" t="n"/>
+      <c r="B73" s="28" t="n"/>
+      <c r="C73" s="28" t="n"/>
+      <c r="D73" s="28" t="n"/>
+      <c r="E73" s="28" t="n"/>
+      <c r="F73" s="28" t="n"/>
+      <c r="G73" s="28" t="n"/>
+      <c r="H73" s="28" t="n"/>
+      <c r="I73" s="28" t="n"/>
+      <c r="J73" s="28" t="n"/>
+      <c r="K73" s="28" t="n"/>
+      <c r="L73" s="28" t="n"/>
+      <c r="M73" s="28" t="n"/>
+      <c r="N73" s="28" t="n"/>
+      <c r="O73" s="28" t="n"/>
+      <c r="P73" s="28" t="n"/>
+      <c r="Q73" s="28" t="n"/>
+      <c r="R73" s="28" t="n"/>
     </row>
     <row r="74">
-      <c r="A74" s="28" t="n"/>
-      <c r="B74" s="28" t="n"/>
-      <c r="C74" s="28" t="n"/>
-      <c r="D74" s="28" t="n"/>
-      <c r="E74" s="28" t="n"/>
-      <c r="F74" s="28" t="n"/>
-      <c r="G74" s="28" t="n"/>
-      <c r="H74" s="28" t="n"/>
-      <c r="I74" s="28" t="n"/>
-      <c r="J74" s="28" t="n"/>
-      <c r="K74" s="28" t="n"/>
-      <c r="L74" s="28" t="n"/>
-      <c r="M74" s="28" t="n"/>
-      <c r="N74" s="28" t="n"/>
-      <c r="O74" s="28" t="n"/>
-      <c r="P74" s="28" t="n"/>
-      <c r="Q74" s="28" t="n"/>
-      <c r="R74" s="28" t="n"/>
+      <c r="A74" s="29" t="n"/>
+      <c r="B74" s="29" t="n"/>
+      <c r="C74" s="29" t="n"/>
+      <c r="D74" s="29" t="n"/>
+      <c r="E74" s="29" t="n"/>
+      <c r="F74" s="29" t="n"/>
+      <c r="G74" s="29" t="n"/>
+      <c r="H74" s="29" t="n"/>
+      <c r="I74" s="29" t="n"/>
+      <c r="J74" s="29" t="n"/>
+      <c r="K74" s="29" t="n"/>
+      <c r="L74" s="29" t="n"/>
+      <c r="M74" s="29" t="n"/>
+      <c r="N74" s="29" t="n"/>
+      <c r="O74" s="29" t="n"/>
+      <c r="P74" s="29" t="n"/>
+      <c r="Q74" s="29" t="n"/>
+      <c r="R74" s="29" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="7" t="inlineStr">
@@ -3485,116 +3493,116 @@
           <t>Números simples</t>
         </is>
       </c>
-      <c r="B76" s="1" t="n"/>
-      <c r="C76" s="29" t="n"/>
+      <c r="B76" s="8" t="n"/>
+      <c r="C76" s="30" t="n"/>
     </row>
     <row r="77">
-      <c r="A77" s="30" t="inlineStr">
+      <c r="A77" s="31" t="inlineStr">
         <is>
           <t>Conversas registradas</t>
         </is>
       </c>
-      <c r="B77" s="31" t="n"/>
-      <c r="C77" s="32">
+      <c r="B77" s="32" t="n"/>
+      <c r="C77" s="33">
         <f>SUMPRODUCT(($A$5:$A$74&lt;&gt;"")*1)</f>
         <v/>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="30" t="inlineStr">
+      <c r="A78" s="31" t="inlineStr">
         <is>
           <t>Média de “pronto para o PS”</t>
         </is>
       </c>
-      <c r="B78" s="31" t="n"/>
-      <c r="C78" s="32">
+      <c r="B78" s="32" t="n"/>
+      <c r="C78" s="33">
         <f>IFERROR(ROUND(AVERAGE($E$5:$E$74),1),"")</f>
         <v/>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="30" t="inlineStr">
+      <c r="A79" s="31" t="inlineStr">
         <is>
           <t>Média de “chance de continuar”</t>
         </is>
       </c>
-      <c r="B79" s="31" t="n"/>
-      <c r="C79" s="32">
+      <c r="B79" s="32" t="n"/>
+      <c r="C79" s="33">
         <f>IFERROR(ROUND(AVERAGE($F$5:$F$74),1),"")</f>
         <v/>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="30" t="inlineStr">
+      <c r="A80" s="31" t="inlineStr">
         <is>
           <t>Membros com chance de continuar 6 ou menos</t>
         </is>
       </c>
-      <c r="B80" s="31" t="n"/>
-      <c r="C80" s="32">
+      <c r="B80" s="32" t="n"/>
+      <c r="C80" s="33">
         <f>COUNTIF($F$5:$F$74,"&lt;=6")</f>
         <v/>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="30" t="inlineStr">
+      <c r="A81" s="31" t="inlineStr">
         <is>
           <t>Membros que não estão entregando</t>
         </is>
       </c>
-      <c r="B81" s="31" t="n"/>
-      <c r="C81" s="32">
+      <c r="B81" s="32" t="n"/>
+      <c r="C81" s="33">
         <f>COUNTIF($D$5:$D$74,"Nao")</f>
         <v/>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="30" t="inlineStr">
+      <c r="A82" s="31" t="inlineStr">
         <is>
           <t>Combinados já feitos</t>
         </is>
       </c>
-      <c r="B82" s="31" t="n"/>
-      <c r="C82" s="32">
+      <c r="B82" s="32" t="n"/>
+      <c r="C82" s="33">
         <f>COUNTIF($R$5:$R$74,"Feito")</f>
         <v/>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="30" t="inlineStr">
+      <c r="A83" s="31" t="inlineStr">
         <is>
           <t>Combinados em aberto</t>
         </is>
       </c>
-      <c r="B83" s="31" t="n"/>
-      <c r="C83" s="32">
+      <c r="B83" s="32" t="n"/>
+      <c r="C83" s="33">
         <f>COUNTIF($R$5:$R$74,"Em aberto")</f>
         <v/>
       </c>
     </row>
     <row r="85" ht="34" customHeight="1">
-      <c r="A85" s="24" t="inlineStr">
+      <c r="A85" s="25" t="inlineStr">
         <is>
           <t>Leitura rápida: nota de continuar 6 ou menos é conversa de retenção nesta semana, não no próximo trimestre. E se o mesmo “aviso ao candidato” aparecer em três conversas diferentes, o problema é do processo, não da pessoa.</t>
         </is>
       </c>
-      <c r="B85" s="25" t="n"/>
-      <c r="C85" s="25" t="n"/>
-      <c r="D85" s="25" t="n"/>
-      <c r="E85" s="25" t="n"/>
-      <c r="F85" s="25" t="n"/>
-      <c r="G85" s="25" t="n"/>
-      <c r="H85" s="25" t="n"/>
-      <c r="I85" s="25" t="n"/>
-      <c r="J85" s="25" t="n"/>
-      <c r="K85" s="25" t="n"/>
-      <c r="L85" s="25" t="n"/>
-      <c r="M85" s="25" t="n"/>
-      <c r="N85" s="25" t="n"/>
-      <c r="O85" s="25" t="n"/>
-      <c r="P85" s="25" t="n"/>
-      <c r="Q85" s="25" t="n"/>
-      <c r="R85" s="25" t="n"/>
+      <c r="B85" s="26" t="n"/>
+      <c r="C85" s="26" t="n"/>
+      <c r="D85" s="26" t="n"/>
+      <c r="E85" s="26" t="n"/>
+      <c r="F85" s="26" t="n"/>
+      <c r="G85" s="26" t="n"/>
+      <c r="H85" s="26" t="n"/>
+      <c r="I85" s="26" t="n"/>
+      <c r="J85" s="26" t="n"/>
+      <c r="K85" s="26" t="n"/>
+      <c r="L85" s="26" t="n"/>
+      <c r="M85" s="26" t="n"/>
+      <c r="N85" s="26" t="n"/>
+      <c r="O85" s="26" t="n"/>
+      <c r="P85" s="26" t="n"/>
+      <c r="Q85" s="26" t="n"/>
+      <c r="R85" s="26" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="13">
